--- a/frontend/public/data/old_new_pl.xlsx
+++ b/frontend/public/data/old_new_pl.xlsx
@@ -8,17 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\업무인수인계\6.실적보고\2025년\stodashboard\frontend\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A158183D-AE4B-47B0-8FE6-89F3F4253679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57752B8E-1142-4A00-973E-11D1091FF1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="15" windowWidth="29040" windowHeight="15720" xr2:uid="{0C279A8B-39A3-4ED4-B4B9-CA68FBFF28CA}"/>
+    <workbookView xWindow="28680" yWindow="15" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{0C279A8B-39A3-4ED4-B4B9-CA68FBFF28CA}"/>
   </bookViews>
   <sheets>
-    <sheet name="Before" sheetId="1" r:id="rId1"/>
-    <sheet name="after" sheetId="2" r:id="rId2"/>
+    <sheet name="old" sheetId="1" r:id="rId1"/>
+    <sheet name="new" sheetId="2" r:id="rId2"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId3"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_" localSheetId="1" hidden="1">#REF!</definedName>
     <definedName name="_" hidden="1">#REF!</definedName>
@@ -11659,9 +11656,9 @@
     <definedName name="금액">#N/A</definedName>
     <definedName name="금월" localSheetId="1" hidden="1">{#N/A,#N/A,TRUE,"Y생산";#N/A,#N/A,TRUE,"Y판매";#N/A,#N/A,TRUE,"Y총물량";#N/A,#N/A,TRUE,"Y능력";#N/A,#N/A,TRUE,"YKD"}</definedName>
     <definedName name="금월" hidden="1">{#N/A,#N/A,TRUE,"Y생산";#N/A,#N/A,TRUE,"Y판매";#N/A,#N/A,TRUE,"Y총물량";#N/A,#N/A,TRUE,"Y능력";#N/A,#N/A,TRUE,"YKD"}</definedName>
-    <definedName name="금월요금1" localSheetId="1">ROUND(after!사용량1-after!사용량1*(전월일수-#REF!+1)/전월일수,0)*사용요금11</definedName>
+    <definedName name="금월요금1" localSheetId="1">ROUND(new!사용량1-new!사용량1*(전월일수-#REF!+1)/전월일수,0)*사용요금11</definedName>
     <definedName name="금월요금1">ROUND(사용량1-사용량1*(전월일수-#REF!+1)/전월일수,0)*사용요금11</definedName>
-    <definedName name="금월요금2" localSheetId="1">ROUND(after!사용량2-after!사용량2*(전월일수-#REF!+1)/전월일수,0)*사용요금21</definedName>
+    <definedName name="금월요금2" localSheetId="1">ROUND(new!사용량2-new!사용량2*(전월일수-#REF!+1)/전월일수,0)*사용요금21</definedName>
     <definedName name="금월요금2">ROUND(사용량2-사용량2*(전월일수-#REF!+1)/전월일수,0)*사용요금21</definedName>
     <definedName name="금월요금3">#N/A</definedName>
     <definedName name="금융기관" localSheetId="1">#REF!</definedName>
@@ -11775,9 +11772,9 @@
     <definedName name="기남이가보냄">#REF!</definedName>
     <definedName name="기말" localSheetId="1">#REF!</definedName>
     <definedName name="기말">#REF!</definedName>
-    <definedName name="기본요금1" localSheetId="1">VLOOKUP(#REF!,after!요금,2)</definedName>
+    <definedName name="기본요금1" localSheetId="1">VLOOKUP(#REF!,new!요금,2)</definedName>
     <definedName name="기본요금1">VLOOKUP(#REF!,요금,2)</definedName>
-    <definedName name="기본요금2" localSheetId="1">VLOOKUP(#REF!,after!요금,2)</definedName>
+    <definedName name="기본요금2" localSheetId="1">VLOOKUP(#REF!,new!요금,2)</definedName>
     <definedName name="기본요금2">VLOOKUP(#REF!,요금,2)</definedName>
     <definedName name="기본운영계획1" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"채산3501.XLS";#N/A,#N/A,FALSE,"신조수A.XLS";#N/A,#N/A,FALSE,"신조수b.XLS";#N/A,#N/A,FALSE,"채산3502.XLS";#N/A,#N/A,FALSE,"신조원리.XLS";#N/A,#N/A,FALSE,"신조감가.XLS"}</definedName>
     <definedName name="기본운영계획1" hidden="1">{#N/A,#N/A,FALSE,"채산3501.XLS";#N/A,#N/A,FALSE,"신조수A.XLS";#N/A,#N/A,FALSE,"신조수b.XLS";#N/A,#N/A,FALSE,"채산3502.XLS";#N/A,#N/A,FALSE,"신조원리.XLS";#N/A,#N/A,FALSE,"신조감가.XLS"}</definedName>
@@ -11889,7 +11886,7 @@
     <definedName name="ㄴㄴㄴ_1" hidden="1">{#N/A,#N/A,TRUE,"대 차 대 조 표"}</definedName>
     <definedName name="ㄴㄴㄴㄴ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"단축1";#N/A,#N/A,FALSE,"단축2";#N/A,#N/A,FALSE,"단축3";#N/A,#N/A,FALSE,"장축";#N/A,#N/A,FALSE,"4WD"}</definedName>
     <definedName name="ㄴㄴㄴㄴ" hidden="1">{#N/A,#N/A,FALSE,"단축1";#N/A,#N/A,FALSE,"단축2";#N/A,#N/A,FALSE,"단축3";#N/A,#N/A,FALSE,"장축";#N/A,#N/A,FALSE,"4WD"}</definedName>
-    <definedName name="ㄴㄹ" localSheetId="1">ROUND(after!사용량2*(ㅂㅈ-#REF!+1)/ㅂㅈ,0)*사용</definedName>
+    <definedName name="ㄴㄹ" localSheetId="1">ROUND(new!사용량2*(ㅂㅈ-#REF!+1)/ㅂㅈ,0)*사용</definedName>
     <definedName name="ㄴㄹ">ROUND(사용량2*(ㅂㅈ-#REF!+1)/ㅂㅈ,0)*사용</definedName>
     <definedName name="ㄴㄹㅇ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"Aging Summary";#N/A,#N/A,FALSE,"Ratio Analysis";#N/A,#N/A,FALSE,"Test 120 Day Accts";#N/A,#N/A,FALSE,"Tickmarks"}</definedName>
     <definedName name="ㄴㄹㅇ" hidden="1">{#N/A,#N/A,FALSE,"Aging Summary";#N/A,#N/A,FALSE,"Ratio Analysis";#N/A,#N/A,FALSE,"Test 120 Day Accts";#N/A,#N/A,FALSE,"Tickmarks"}</definedName>
@@ -12307,7 +12304,7 @@
     <definedName name="ㅁ나ㅣ어리마ㅗㅇ호미오히ㅏ몬이호" hidden="1">{#N/A,#N/A,FALSE,"Aging Summary";#N/A,#N/A,FALSE,"Ratio Analysis";#N/A,#N/A,FALSE,"Test 120 Day Accts";#N/A,#N/A,FALSE,"Tickmarks"}</definedName>
     <definedName name="ㅁㄷ" localSheetId="1" hidden="1">#REF!</definedName>
     <definedName name="ㅁㄷ" hidden="1">#REF!</definedName>
-    <definedName name="ㅁㄹ" localSheetId="1">VLOOKUP(#REF!,after!요금,2)</definedName>
+    <definedName name="ㅁㄹ" localSheetId="1">VLOOKUP(#REF!,new!요금,2)</definedName>
     <definedName name="ㅁㄹ">VLOOKUP(#REF!,요금,2)</definedName>
     <definedName name="ㅁㄹㄹㄹㄹ" localSheetId="1">VLOOKUP(#REF!,#REF!,2)</definedName>
     <definedName name="ㅁㄹㄹㄹㄹ">VLOOKUP(#REF!,#REF!,2)</definedName>
@@ -13738,7 +13735,7 @@
     <definedName name="여유분">#REF!</definedName>
     <definedName name="여이" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"1.CRITERIA";#N/A,#N/A,FALSE,"2.IS";#N/A,#N/A,FALSE,"3.BS";#N/A,#N/A,FALSE,"4.PER PL";#N/A,#N/A,FALSE,"5.INVESTMENT";#N/A,#N/A,FALSE,"6.공문";#N/A,#N/A,FALSE,"7.netinvest"}</definedName>
     <definedName name="여이" hidden="1">{#N/A,#N/A,FALSE,"1.CRITERIA";#N/A,#N/A,FALSE,"2.IS";#N/A,#N/A,FALSE,"3.BS";#N/A,#N/A,FALSE,"4.PER PL";#N/A,#N/A,FALSE,"5.INVESTMENT";#N/A,#N/A,FALSE,"6.공문";#N/A,#N/A,FALSE,"7.netinvest"}</definedName>
-    <definedName name="역률요금1" localSheetId="1">IF(#REF!="저압",0,ROUND(IF(#REF!&gt;0.95,0.05,#REF!-0.9)*after!기본요금1*MAX(피크치1,#REF!,#REF!*0.3),0))</definedName>
+    <definedName name="역률요금1" localSheetId="1">IF(#REF!="저압",0,ROUND(IF(#REF!&gt;0.95,0.05,#REF!-0.9)*new!기본요금1*MAX(피크치1,#REF!,#REF!*0.3),0))</definedName>
     <definedName name="역률요금1">IF(#REF!="저압",0,ROUND(IF(#REF!&gt;0.95,0.05,#REF!-0.9)*기본요금1*MAX(피크치1,#REF!,#REF!*0.3),0))</definedName>
     <definedName name="역삼동각지" localSheetId="1">#REF!</definedName>
     <definedName name="역삼동각지">#REF!</definedName>
@@ -14459,9 +14456,9 @@
     <definedName name="전산장비" hidden="1">{"'Sheet1'!$A$1:$H$36"}</definedName>
     <definedName name="전신전화" localSheetId="1">#REF!</definedName>
     <definedName name="전신전화">#REF!</definedName>
-    <definedName name="전월요금1" localSheetId="1">ROUND(after!사용량1*(전월일수-#REF!+1)/전월일수,0)*사용요금10</definedName>
+    <definedName name="전월요금1" localSheetId="1">ROUND(new!사용량1*(전월일수-#REF!+1)/전월일수,0)*사용요금10</definedName>
     <definedName name="전월요금1">ROUND(사용량1*(전월일수-#REF!+1)/전월일수,0)*사용요금10</definedName>
-    <definedName name="전월요금2" localSheetId="1">ROUND(after!사용량2*(전월일수-#REF!+1)/전월일수,0)*사용요금20</definedName>
+    <definedName name="전월요금2" localSheetId="1">ROUND(new!사용량2*(전월일수-#REF!+1)/전월일수,0)*사용요금20</definedName>
     <definedName name="전월요금2">ROUND(사용량2*(전월일수-#REF!+1)/전월일수,0)*사용요금20</definedName>
     <definedName name="전월일수">#N/A</definedName>
     <definedName name="전입액" localSheetId="1">#REF!</definedName>
@@ -15621,7 +15618,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="38">
   <si>
     <t>＊Profit &amp; Loss</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -15632,14 +15629,6 @@
   </si>
   <si>
     <t>Content</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025 Total</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -15759,38 +15748,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>6. Other Income(Expense)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Interest</t>
-  </si>
-  <si>
-    <t>Other Income (BTL)</t>
-  </si>
-  <si>
-    <t>Other Expense</t>
-  </si>
-  <si>
-    <t>Other Misc</t>
-  </si>
-  <si>
-    <t>Realized Gain / Loss</t>
-  </si>
-  <si>
-    <t>Tax</t>
-  </si>
-  <si>
-    <t>Unrealized Gain / Loss</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>Net Profit</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>NEW 합계</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -15803,24 +15760,22 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="15">
+  <numFmts count="13">
     <numFmt numFmtId="176" formatCode="&quot;$&quot;#,##0,;\(&quot;$&quot;#,##0,\);&quot;--&quot;"/>
     <numFmt numFmtId="177" formatCode="mmm\-yy&quot;F&quot;"/>
-    <numFmt numFmtId="178" formatCode="mmm\-yy&quot;A&quot;"/>
-    <numFmt numFmtId="179" formatCode="\$#,##0,\ ;[Red]\-\$#,##0,\ ;&quot;-&quot;\ "/>
-    <numFmt numFmtId="180" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="181" formatCode="0.0%;;&quot;-&quot;\ "/>
-    <numFmt numFmtId="182" formatCode="#.#\ ;;&quot;-&quot;\ "/>
-    <numFmt numFmtId="183" formatCode="#,##0.0;\(#,##0.0\);&quot;--&quot;"/>
-    <numFmt numFmtId="184" formatCode="0.0%\ ;[Red]\-0.0%\ ;&quot;-&quot;\ "/>
-    <numFmt numFmtId="186" formatCode="0.0%"/>
-    <numFmt numFmtId="187" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="188" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="189" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="190" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="191" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="\$#,##0,\ ;[Red]\-\$#,##0,\ ;&quot;-&quot;\ "/>
+    <numFmt numFmtId="179" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="180" formatCode="0.0%;;&quot;-&quot;\ "/>
+    <numFmt numFmtId="181" formatCode="#,##0.0;\(#,##0.0\);&quot;--&quot;"/>
+    <numFmt numFmtId="182" formatCode="0.0%\ ;[Red]\-0.0%\ ;&quot;-&quot;\ "/>
+    <numFmt numFmtId="183" formatCode="0.0%"/>
+    <numFmt numFmtId="184" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="185" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="186" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="187" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="188" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -15930,16 +15885,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -15949,12 +15896,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -15977,7 +15918,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -16003,17 +15944,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -16279,82 +16209,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFF0000"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFFF0000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFF0000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFFF0000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFF0000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
@@ -16374,11 +16228,11 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="189" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="184" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -16397,85 +16251,49 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="8" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="177" fontId="8" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="8" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="3" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="3" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="4" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="4" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="4" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
-    <xf numFmtId="179" fontId="11" fillId="4" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="12" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="4" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="4" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="11" fillId="3" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -16484,25 +16302,19 @@
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="4" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="4" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="3" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="4" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="4" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="3" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -16511,181 +16323,103 @@
     <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="13" fillId="3" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="179" fontId="13" fillId="4" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="13" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="13" fillId="4" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="13" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="13" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="8" fillId="4" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="8" fillId="4" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="3" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="13" fillId="4" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="13" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
+    <xf numFmtId="181" fontId="8" fillId="4" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="13" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="8" fillId="4" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="5" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="13" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="5" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="13" fillId="4" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="8" fillId="5" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="13" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="8" fillId="5" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="8" fillId="5" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="8" fillId="5" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="8" fillId="5" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="4" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="8" fillId="5" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="13" fillId="4" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="8" fillId="5" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="13" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="8" fillId="2" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="13" fillId="4" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="185" fontId="2" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="8" fillId="5" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="8" fillId="5" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="8" fillId="5" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="8" fillId="5" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="6" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="186" fontId="2" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="6" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="6" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="6" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="8" fillId="6" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="8" fillId="6" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="8" fillId="6" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="8" fillId="6" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="8" fillId="6" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="8" fillId="6" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="4" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="4" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="4" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="4" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="6" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="6" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="8" fillId="6" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="8" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="8" fillId="6" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="2" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="186" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="188" fontId="2" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="189" fontId="2" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="190" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -16695,14 +16429,14 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="191" fontId="2" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="2" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="188" fontId="15" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -16724,32 +16458,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="PL_before"/>
-      <sheetName val="PL_after"/>
-      <sheetName val="Inven_before"/>
-      <sheetName val="Inven_after"/>
-      <sheetName val="Cash_before"/>
-      <sheetName val="Cash_after"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17072,7 +16780,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="B1:Q78"/>
+  <dimension ref="B1:Q67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="2.625" style="1" customWidth="1"/>
@@ -17106,1792 +16814,1549 @@
       </c>
     </row>
     <row r="4" spans="2:17" ht="15" customHeight="1" thickBot="1">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="10"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="7"/>
     </row>
     <row r="5" spans="2:17" ht="15" customHeight="1">
-      <c r="B5" s="11"/>
-      <c r="C5" s="14">
+      <c r="B5" s="68"/>
+      <c r="C5" s="8">
         <v>46266</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="8">
         <f t="shared" ref="D5:F5" si="0">EDATE(C5,1)</f>
         <v>46296</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="8">
         <f t="shared" si="0"/>
         <v>46327</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="8">
         <f t="shared" si="0"/>
         <v>46357</v>
       </c>
-      <c r="G5" s="15" t="s">
-        <v>49</v>
+      <c r="G5" s="9" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="2:17" ht="15" customHeight="1">
-      <c r="B6" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="19">
+      <c r="B6" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="11">
         <f t="shared" ref="C6:G6" si="1">SUM(C7,C15)</f>
         <v>4430367.2809627801</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="11">
         <f t="shared" si="1"/>
         <v>3828322.2936669569</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="11">
         <f t="shared" si="1"/>
         <v>6482849.043328573</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="11">
         <f t="shared" si="1"/>
         <v>6483078.9437603317</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="12">
         <f t="shared" si="1"/>
         <v>21224617.561718643</v>
       </c>
     </row>
     <row r="7" spans="2:17" ht="15" customHeight="1">
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="15">
+        <v>3888798.2809627801</v>
+      </c>
+      <c r="D7" s="15">
+        <v>3422176.2936669569</v>
+      </c>
+      <c r="E7" s="15">
+        <v>6321719.043328573</v>
+      </c>
+      <c r="F7" s="15">
+        <v>6321948.9437603317</v>
+      </c>
+      <c r="G7" s="16">
+        <f t="shared" ref="G7:G21" si="2">SUM(C7:F7)</f>
+        <v>19954642.561718643</v>
+      </c>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+    </row>
+    <row r="8" spans="2:17" s="21" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B8" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="19">
+        <v>951075.00000000035</v>
+      </c>
+      <c r="D8" s="19">
+        <v>951075.00000000023</v>
+      </c>
+      <c r="E8" s="19">
+        <v>1585125.0000000005</v>
+      </c>
+      <c r="F8" s="19">
+        <v>1585125.0000000005</v>
+      </c>
+      <c r="G8" s="20">
+        <f t="shared" si="2"/>
+        <v>5072400.0000000019</v>
+      </c>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+    </row>
+    <row r="9" spans="2:17" s="21" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B9" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="25">
-        <v>3888798.2809627801</v>
-      </c>
-      <c r="D7" s="25">
-        <v>3422176.2936669569</v>
-      </c>
-      <c r="E7" s="25">
-        <v>6321719.043328573</v>
-      </c>
-      <c r="F7" s="25">
-        <v>6321948.9437603317</v>
-      </c>
-      <c r="G7" s="26">
-        <f>SUM(C7:F7)</f>
-        <v>19954642.561718643</v>
-      </c>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="27"/>
-      <c r="M7" s="27"/>
-      <c r="N7" s="27"/>
-      <c r="O7" s="27"/>
+      <c r="C9" s="19">
+        <v>1030000.0000000002</v>
+      </c>
+      <c r="D9" s="19">
+        <v>875500.00000000012</v>
+      </c>
+      <c r="E9" s="19">
+        <v>2060000.0000000005</v>
+      </c>
+      <c r="F9" s="19">
+        <v>2060000.0000000005</v>
+      </c>
+      <c r="G9" s="20">
+        <f t="shared" si="2"/>
+        <v>6025500.0000000019</v>
+      </c>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
     </row>
-    <row r="8" spans="2:17" s="33" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B8" s="28" t="s">
+    <row r="10" spans="2:17" s="21" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B10" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="31">
-        <v>951075.00000000035</v>
-      </c>
-      <c r="D8" s="31">
-        <v>951075.00000000023</v>
-      </c>
-      <c r="E8" s="31">
-        <v>1585125.0000000005</v>
-      </c>
-      <c r="F8" s="31">
-        <v>1585125.0000000005</v>
-      </c>
-      <c r="G8" s="32">
-        <f>SUM(C8:F8)</f>
-        <v>5072400.0000000019</v>
-      </c>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="34"/>
-      <c r="M8" s="34"/>
-      <c r="N8" s="34"/>
-      <c r="O8" s="34"/>
-      <c r="P8" s="34"/>
+      <c r="C10" s="19">
+        <v>1236474.4916745084</v>
+      </c>
+      <c r="D10" s="19">
+        <v>989179.59333960654</v>
+      </c>
+      <c r="E10" s="19">
+        <v>1545593.1145931352</v>
+      </c>
+      <c r="F10" s="19">
+        <v>1545593.1145931352</v>
+      </c>
+      <c r="G10" s="20">
+        <f t="shared" si="2"/>
+        <v>5316840.3142003855</v>
+      </c>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
     </row>
-    <row r="9" spans="2:17" s="33" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B9" s="28" t="s">
+    <row r="11" spans="2:17" s="21" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B11" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="31">
-        <v>1030000.0000000002</v>
-      </c>
-      <c r="D9" s="31">
-        <v>875500.00000000012</v>
-      </c>
-      <c r="E9" s="31">
-        <v>2060000.0000000005</v>
-      </c>
-      <c r="F9" s="31">
-        <v>2060000.0000000005</v>
-      </c>
-      <c r="G9" s="32">
-        <f>SUM(C9:F9)</f>
-        <v>6025500.0000000019</v>
-      </c>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="34"/>
-      <c r="M9" s="34"/>
-      <c r="N9" s="34"/>
-      <c r="O9" s="34"/>
+      <c r="C11" s="19">
+        <v>476899.99632068886</v>
+      </c>
+      <c r="D11" s="19">
+        <v>476899.99632068886</v>
+      </c>
+      <c r="E11" s="19">
+        <v>572279.99558482657</v>
+      </c>
+      <c r="F11" s="19">
+        <v>572279.99558482657</v>
+      </c>
+      <c r="G11" s="20">
+        <f t="shared" si="2"/>
+        <v>2098359.9838110306</v>
+      </c>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
     </row>
-    <row r="10" spans="2:17" s="33" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B10" s="28" t="s">
+    <row r="12" spans="2:17" s="21" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B12" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="31">
-        <v>1236474.4916745084</v>
-      </c>
-      <c r="D10" s="31">
-        <v>989179.59333960654</v>
-      </c>
-      <c r="E10" s="31">
-        <v>1545593.1145931352</v>
-      </c>
-      <c r="F10" s="31">
-        <v>1545593.1145931352</v>
-      </c>
-      <c r="G10" s="32">
-        <f>SUM(C10:F10)</f>
-        <v>5316840.3142003855</v>
-      </c>
-      <c r="I10" s="34"/>
-      <c r="J10" s="34"/>
-      <c r="K10" s="34"/>
-      <c r="L10" s="34"/>
-      <c r="M10" s="34"/>
-      <c r="N10" s="34"/>
-      <c r="O10" s="34"/>
+      <c r="C12" s="19">
+        <v>94974.572917665355</v>
+      </c>
+      <c r="D12" s="19">
+        <v>95204.473349422682</v>
+      </c>
+      <c r="E12" s="19">
+        <v>94974.572917664424</v>
+      </c>
+      <c r="F12" s="19">
+        <v>95204.473349423148</v>
+      </c>
+      <c r="G12" s="20">
+        <f t="shared" si="2"/>
+        <v>380358.09253417561</v>
+      </c>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
     </row>
-    <row r="11" spans="2:17" s="33" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B11" s="28" t="s">
+    <row r="13" spans="2:17" s="21" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B13" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="31">
-        <v>476899.99632068886</v>
-      </c>
-      <c r="D11" s="31">
-        <v>476899.99632068886</v>
-      </c>
-      <c r="E11" s="31">
-        <v>572279.99558482657</v>
-      </c>
-      <c r="F11" s="31">
-        <v>572279.99558482657</v>
-      </c>
-      <c r="G11" s="32">
-        <f>SUM(C11:F11)</f>
-        <v>2098359.9838110306</v>
-      </c>
-      <c r="I11" s="34"/>
-      <c r="J11" s="34"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="34"/>
-      <c r="M11" s="34"/>
-      <c r="N11" s="34"/>
-      <c r="O11" s="34"/>
+      <c r="C13" s="19">
+        <v>99374.220049916839</v>
+      </c>
+      <c r="D13" s="19">
+        <v>34317.230657237946</v>
+      </c>
+      <c r="E13" s="19">
+        <v>463746.36023294518</v>
+      </c>
+      <c r="F13" s="19">
+        <v>463746.36023294518</v>
+      </c>
+      <c r="G13" s="20">
+        <f t="shared" si="2"/>
+        <v>1061184.1711730452</v>
+      </c>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
     </row>
-    <row r="12" spans="2:17" s="33" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B12" s="28" t="s">
+    <row r="14" spans="2:17" s="21" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B14" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="31">
-        <v>94974.572917665355</v>
-      </c>
-      <c r="D12" s="31">
-        <v>95204.473349422682</v>
-      </c>
-      <c r="E12" s="31">
-        <v>94974.572917664424</v>
-      </c>
-      <c r="F12" s="31">
-        <v>95204.473349423148</v>
-      </c>
-      <c r="G12" s="32">
-        <f>SUM(C12:F12)</f>
-        <v>380358.09253417561</v>
-      </c>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="34"/>
-      <c r="M12" s="34"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="34"/>
-    </row>
-    <row r="13" spans="2:17" s="33" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B13" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="31">
-        <v>99374.220049916839</v>
-      </c>
-      <c r="D13" s="31">
-        <v>34317.230657237946</v>
-      </c>
-      <c r="E13" s="31">
-        <v>463746.36023294518</v>
-      </c>
-      <c r="F13" s="31">
-        <v>463746.36023294518</v>
-      </c>
-      <c r="G13" s="32">
-        <f>SUM(C13:F13)</f>
-        <v>1061184.1711730452</v>
-      </c>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="34"/>
-      <c r="N13" s="34"/>
-      <c r="O13" s="34"/>
-    </row>
-    <row r="14" spans="2:17" s="33" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B14" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="31">
+      <c r="C14" s="19">
         <v>0</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="19">
         <v>0</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="19">
         <v>0</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="19">
         <v>0</v>
       </c>
-      <c r="G14" s="32">
-        <f>SUM(C14:F14)</f>
+      <c r="G14" s="20">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I14" s="34"/>
-      <c r="J14" s="34"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="34"/>
-      <c r="M14" s="34"/>
-      <c r="N14" s="34"/>
-      <c r="O14" s="34"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
     </row>
     <row r="15" spans="2:17" ht="15" customHeight="1">
-      <c r="B15" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="39">
+      <c r="B15" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="25">
         <v>541569</v>
       </c>
-      <c r="D15" s="39">
+      <c r="D15" s="25">
         <v>406146</v>
       </c>
-      <c r="E15" s="39">
+      <c r="E15" s="25">
         <v>161130</v>
       </c>
-      <c r="F15" s="40">
+      <c r="F15" s="26">
         <v>161130</v>
       </c>
-      <c r="G15" s="41">
-        <f>SUM(C15:F15)</f>
+      <c r="G15" s="27">
+        <f t="shared" si="2"/>
         <v>1269975</v>
       </c>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="42"/>
-      <c r="Q15" s="42"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="28"/>
+      <c r="Q15" s="28"/>
     </row>
-    <row r="16" spans="2:17" s="33" customFormat="1" ht="15" customHeight="1" outlineLevel="2">
-      <c r="B16" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="31">
-        <f t="shared" ref="C16:F16" si="2">C15</f>
+    <row r="16" spans="2:17" s="21" customFormat="1" ht="15" customHeight="1" outlineLevel="2">
+      <c r="B16" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="19">
+        <f t="shared" ref="C16:F16" si="3">C15</f>
         <v>541569</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="19">
+        <f t="shared" si="3"/>
+        <v>406146</v>
+      </c>
+      <c r="E16" s="19">
+        <f t="shared" si="3"/>
+        <v>161130</v>
+      </c>
+      <c r="F16" s="19">
+        <f t="shared" si="3"/>
+        <v>161130</v>
+      </c>
+      <c r="G16" s="20">
         <f t="shared" si="2"/>
-        <v>406146</v>
-      </c>
-      <c r="E16" s="31">
-        <f t="shared" si="2"/>
-        <v>161130</v>
-      </c>
-      <c r="F16" s="31">
-        <f t="shared" si="2"/>
-        <v>161130</v>
-      </c>
-      <c r="G16" s="32">
-        <f>SUM(C16:F16)</f>
         <v>1269975</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
     </row>
-    <row r="17" spans="2:17" s="33" customFormat="1" ht="15" customHeight="1" outlineLevel="2">
-      <c r="B17" s="28" t="s">
+    <row r="17" spans="2:17" s="21" customFormat="1" ht="15" customHeight="1" outlineLevel="2">
+      <c r="B17" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="19">
+        <v>0</v>
+      </c>
+      <c r="D17" s="19">
+        <v>0</v>
+      </c>
+      <c r="E17" s="19">
+        <v>0</v>
+      </c>
+      <c r="F17" s="19">
+        <v>0</v>
+      </c>
+      <c r="G17" s="20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="29"/>
+    </row>
+    <row r="18" spans="2:17" s="21" customFormat="1" ht="15" customHeight="1" outlineLevel="2">
+      <c r="B18" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="19">
+        <v>0</v>
+      </c>
+      <c r="D18" s="19">
+        <v>0</v>
+      </c>
+      <c r="E18" s="19">
+        <v>0</v>
+      </c>
+      <c r="F18" s="19">
+        <v>0</v>
+      </c>
+      <c r="G18" s="20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
+      <c r="N18" s="29"/>
+      <c r="O18" s="29"/>
+    </row>
+    <row r="19" spans="2:17" s="21" customFormat="1" ht="15" customHeight="1" outlineLevel="2">
+      <c r="B19" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C19" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D19" s="19">
         <v>0</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E19" s="19">
         <v>0</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F19" s="19">
         <v>0</v>
       </c>
-      <c r="G17" s="32">
-        <f>SUM(C17:F17)</f>
+      <c r="G19" s="20">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I17" s="43"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="43"/>
-      <c r="L17" s="43"/>
-      <c r="M17" s="43"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="43"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="29"/>
+      <c r="L19" s="29"/>
+      <c r="M19" s="29"/>
+      <c r="N19" s="29"/>
+      <c r="O19" s="29"/>
     </row>
-    <row r="18" spans="2:17" s="33" customFormat="1" ht="15" customHeight="1" outlineLevel="2">
-      <c r="B18" s="28" t="s">
+    <row r="20" spans="2:17" s="21" customFormat="1" ht="15" customHeight="1" outlineLevel="2">
+      <c r="B20" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="31">
+      <c r="D20" s="19">
         <v>0</v>
       </c>
-      <c r="E18" s="31">
+      <c r="E20" s="19">
         <v>0</v>
       </c>
-      <c r="F18" s="31">
+      <c r="F20" s="19">
         <v>0</v>
       </c>
-      <c r="G18" s="32">
-        <f>SUM(C18:F18)</f>
+      <c r="G20" s="20">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="43"/>
-      <c r="M18" s="43"/>
-      <c r="N18" s="43"/>
-      <c r="O18" s="43"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
+      <c r="O20" s="29"/>
     </row>
-    <row r="19" spans="2:17" s="33" customFormat="1" ht="15" customHeight="1" outlineLevel="2">
-      <c r="B19" s="28" t="s">
+    <row r="21" spans="2:17" s="21" customFormat="1" ht="15" customHeight="1" outlineLevel="2">
+      <c r="B21" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C21" s="19">
         <v>0</v>
       </c>
-      <c r="D19" s="31">
+      <c r="D21" s="19">
         <v>0</v>
       </c>
-      <c r="E19" s="31">
+      <c r="E21" s="19">
         <v>0</v>
       </c>
-      <c r="F19" s="31">
+      <c r="F21" s="19">
         <v>0</v>
       </c>
-      <c r="G19" s="32">
-        <f>SUM(C19:F19)</f>
+      <c r="G21" s="20">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I19" s="43"/>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
-      <c r="L19" s="43"/>
-      <c r="M19" s="43"/>
-      <c r="N19" s="43"/>
-      <c r="O19" s="43"/>
-    </row>
-    <row r="20" spans="2:17" s="33" customFormat="1" ht="15" customHeight="1" outlineLevel="2">
-      <c r="B20" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="31">
-        <v>0</v>
-      </c>
-      <c r="D20" s="31">
-        <v>0</v>
-      </c>
-      <c r="E20" s="31">
-        <v>0</v>
-      </c>
-      <c r="F20" s="31">
-        <v>0</v>
-      </c>
-      <c r="G20" s="32">
-        <f>SUM(C20:F20)</f>
-        <v>0</v>
-      </c>
-      <c r="I20" s="43"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="43"/>
-      <c r="M20" s="43"/>
-      <c r="N20" s="43"/>
-      <c r="O20" s="43"/>
-    </row>
-    <row r="21" spans="2:17" s="33" customFormat="1" ht="15" customHeight="1" outlineLevel="2">
-      <c r="B21" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="31">
-        <v>0</v>
-      </c>
-      <c r="D21" s="31">
-        <v>0</v>
-      </c>
-      <c r="E21" s="31">
-        <v>0</v>
-      </c>
-      <c r="F21" s="31">
-        <v>0</v>
-      </c>
-      <c r="G21" s="32">
-        <f>SUM(C21:F21)</f>
-        <v>0</v>
-      </c>
-      <c r="I21" s="43"/>
-      <c r="J21" s="43"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="43"/>
-      <c r="M21" s="43"/>
-      <c r="N21" s="43"/>
-      <c r="O21" s="43"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="29"/>
+      <c r="K21" s="29"/>
+      <c r="L21" s="29"/>
+      <c r="M21" s="29"/>
+      <c r="N21" s="29"/>
+      <c r="O21" s="29"/>
     </row>
     <row r="22" spans="2:17" ht="15" customHeight="1">
-      <c r="B22" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="47">
-        <f t="shared" ref="C22:G22" si="3">C23+C31+C38+C39</f>
+      <c r="B22" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="31">
+        <f t="shared" ref="C22:G22" si="4">C23+C31+C38+C39</f>
         <v>2754878.4283693423</v>
       </c>
-      <c r="D22" s="47">
-        <f t="shared" si="3"/>
+      <c r="D22" s="31">
+        <f t="shared" si="4"/>
         <v>2330472.1337369638</v>
       </c>
-      <c r="E22" s="47">
-        <f t="shared" si="3"/>
+      <c r="E22" s="31">
+        <f t="shared" si="4"/>
         <v>3767365.4278565072</v>
       </c>
-      <c r="F22" s="47">
-        <f t="shared" si="3"/>
+      <c r="F22" s="31">
+        <f t="shared" si="4"/>
         <v>3813915.3060335843</v>
       </c>
-      <c r="G22" s="48">
-        <f t="shared" si="3"/>
+      <c r="G22" s="32">
+        <f t="shared" si="4"/>
         <v>12666631.295996398</v>
       </c>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="43"/>
-      <c r="M22" s="43"/>
-      <c r="N22" s="43"/>
-      <c r="O22" s="43"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="29"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="29"/>
+      <c r="N22" s="29"/>
+      <c r="O22" s="29"/>
     </row>
     <row r="23" spans="2:17" ht="15" customHeight="1">
-      <c r="B23" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="24">
+      <c r="B23" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="14">
         <v>2455359.2430000002</v>
       </c>
-      <c r="D23" s="24">
+      <c r="D23" s="14">
         <v>2126830.1720000007</v>
       </c>
-      <c r="E23" s="24">
+      <c r="E23" s="14">
         <v>3653491.7430000002</v>
       </c>
-      <c r="F23" s="24">
+      <c r="F23" s="14">
         <v>3653537.6720000003</v>
       </c>
-      <c r="G23" s="26">
-        <f>SUM(C23:F23)</f>
+      <c r="G23" s="16">
+        <f t="shared" ref="G23:G39" si="5">SUM(C23:F23)</f>
         <v>11889218.830000002</v>
       </c>
-      <c r="I23" s="43"/>
-      <c r="J23" s="43"/>
-      <c r="K23" s="43"/>
-      <c r="L23" s="43"/>
-      <c r="M23" s="43"/>
-      <c r="N23" s="43"/>
-      <c r="O23" s="43"/>
-      <c r="P23" s="49"/>
-      <c r="Q23" s="49"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
+      <c r="N23" s="29"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="33"/>
+      <c r="Q23" s="33"/>
     </row>
     <row r="24" spans="2:17" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B24" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="31">
+      <c r="B24" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="19">
         <v>855967.5</v>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="19">
         <v>855967.5</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="19">
         <v>1030375.0000000001</v>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="19">
         <v>1030375.0000000001</v>
       </c>
-      <c r="G24" s="32">
-        <f>SUM(C24:F24)</f>
+      <c r="G24" s="20">
+        <f t="shared" si="5"/>
         <v>3772685</v>
       </c>
-      <c r="I24" s="49"/>
-      <c r="J24" s="49"/>
-      <c r="K24" s="49"/>
-      <c r="L24" s="49"/>
-      <c r="M24" s="49"/>
-      <c r="N24" s="49"/>
-      <c r="O24" s="49"/>
-      <c r="P24" s="49"/>
-      <c r="Q24" s="49"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
+      <c r="N24" s="33"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="33"/>
+      <c r="Q24" s="33"/>
     </row>
     <row r="25" spans="2:17" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B25" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="31">
+      <c r="B25" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="19">
         <v>700000</v>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="19">
         <v>552500</v>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="19">
         <v>1300000</v>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="19">
         <v>1300000</v>
       </c>
-      <c r="G25" s="32">
-        <f>SUM(C25:F25)</f>
+      <c r="G25" s="20">
+        <f t="shared" si="5"/>
         <v>3852500</v>
       </c>
-      <c r="I25" s="49"/>
-      <c r="J25" s="49"/>
-      <c r="K25" s="49"/>
-      <c r="L25" s="49"/>
-      <c r="M25" s="49"/>
-      <c r="N25" s="49"/>
-      <c r="O25" s="49"/>
-      <c r="P25" s="49"/>
-      <c r="Q25" s="49"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="33"/>
+      <c r="M25" s="33"/>
+      <c r="N25" s="33"/>
+      <c r="O25" s="33"/>
+      <c r="P25" s="33"/>
+      <c r="Q25" s="33"/>
     </row>
     <row r="26" spans="2:17" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B26" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" s="31">
+      <c r="B26" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="19">
         <v>598499.99999999988</v>
       </c>
-      <c r="D26" s="31">
+      <c r="D26" s="19">
         <v>478799.99999999988</v>
       </c>
-      <c r="E26" s="31">
+      <c r="E26" s="19">
         <v>714875</v>
       </c>
-      <c r="F26" s="31">
+      <c r="F26" s="19">
         <v>714875</v>
       </c>
-      <c r="G26" s="32">
-        <f>SUM(C26:F26)</f>
+      <c r="G26" s="20">
+        <f t="shared" si="5"/>
         <v>2507050</v>
       </c>
-      <c r="I26" s="49"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="49"/>
-      <c r="L26" s="49"/>
-      <c r="M26" s="49"/>
-      <c r="N26" s="49"/>
-      <c r="O26" s="49"/>
-      <c r="P26" s="49"/>
-      <c r="Q26" s="49"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
+      <c r="N26" s="33"/>
+      <c r="O26" s="33"/>
+      <c r="P26" s="33"/>
+      <c r="Q26" s="33"/>
     </row>
     <row r="27" spans="2:17" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B27" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="31">
+      <c r="B27" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="19">
         <v>167999.99999999994</v>
       </c>
-      <c r="D27" s="31">
+      <c r="D27" s="19">
         <v>167999.99999999994</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="19">
         <v>201599.99999999991</v>
       </c>
-      <c r="F27" s="31">
+      <c r="F27" s="19">
         <v>201599.99999999991</v>
       </c>
-      <c r="G27" s="32">
-        <f>SUM(C27:F27)</f>
+      <c r="G27" s="20">
+        <f t="shared" si="5"/>
         <v>739199.99999999965</v>
       </c>
-      <c r="I27" s="49"/>
-      <c r="J27" s="49"/>
-      <c r="K27" s="49"/>
-      <c r="L27" s="49"/>
-      <c r="M27" s="49"/>
-      <c r="N27" s="49"/>
-      <c r="O27" s="49"/>
-      <c r="P27" s="49"/>
-      <c r="Q27" s="49"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
+      <c r="N27" s="33"/>
+      <c r="O27" s="33"/>
+      <c r="P27" s="33"/>
+      <c r="Q27" s="33"/>
     </row>
     <row r="28" spans="2:17" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B28" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="31">
+      <c r="B28" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="19">
         <v>39141.74300000025</v>
       </c>
-      <c r="D28" s="31">
+      <c r="D28" s="19">
         <v>39187.672000000719</v>
       </c>
-      <c r="E28" s="31">
+      <c r="E28" s="19">
         <v>39141.74300000025</v>
       </c>
-      <c r="F28" s="31">
+      <c r="F28" s="19">
         <v>39187.672000000253</v>
       </c>
-      <c r="G28" s="32">
-        <f>SUM(C28:F28)</f>
+      <c r="G28" s="20">
+        <f t="shared" si="5"/>
         <v>156658.83000000147</v>
       </c>
-      <c r="I28" s="49"/>
-      <c r="J28" s="49"/>
-      <c r="K28" s="49"/>
-      <c r="L28" s="49"/>
-      <c r="M28" s="49"/>
-      <c r="N28" s="49"/>
-      <c r="O28" s="49"/>
-      <c r="P28" s="49"/>
-      <c r="Q28" s="49"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
+      <c r="N28" s="33"/>
+      <c r="O28" s="33"/>
+      <c r="P28" s="33"/>
+      <c r="Q28" s="33"/>
     </row>
     <row r="29" spans="2:17" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B29" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="31">
+      <c r="B29" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="19">
         <v>93750</v>
       </c>
-      <c r="D29" s="31">
+      <c r="D29" s="19">
         <v>32375</v>
       </c>
-      <c r="E29" s="31">
+      <c r="E29" s="19">
         <v>367500</v>
       </c>
-      <c r="F29" s="31">
+      <c r="F29" s="19">
         <v>367500</v>
       </c>
-      <c r="G29" s="32">
-        <f>SUM(C29:F29)</f>
+      <c r="G29" s="20">
+        <f t="shared" si="5"/>
         <v>861125</v>
       </c>
-      <c r="I29" s="49"/>
-      <c r="J29" s="49"/>
-      <c r="K29" s="49"/>
-      <c r="L29" s="49"/>
-      <c r="M29" s="49"/>
-      <c r="N29" s="49"/>
-      <c r="O29" s="49"/>
-      <c r="P29" s="49"/>
-      <c r="Q29" s="49"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="33"/>
+      <c r="N29" s="33"/>
+      <c r="O29" s="33"/>
+      <c r="P29" s="33"/>
+      <c r="Q29" s="33"/>
     </row>
     <row r="30" spans="2:17" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B30" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" s="31">
+      <c r="B30" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="19">
         <v>0</v>
       </c>
-      <c r="D30" s="31">
+      <c r="D30" s="19">
         <v>0</v>
       </c>
-      <c r="E30" s="31">
+      <c r="E30" s="19">
         <v>0</v>
       </c>
-      <c r="F30" s="31">
+      <c r="F30" s="19">
         <v>0</v>
       </c>
-      <c r="G30" s="32">
-        <f>SUM(C30:F30)</f>
+      <c r="G30" s="20">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="I30" s="49"/>
-      <c r="J30" s="49"/>
-      <c r="K30" s="49"/>
-      <c r="L30" s="49"/>
-      <c r="M30" s="49"/>
-      <c r="N30" s="49"/>
-      <c r="O30" s="49"/>
-      <c r="P30" s="49"/>
-      <c r="Q30" s="49"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="33"/>
+      <c r="M30" s="33"/>
+      <c r="N30" s="33"/>
+      <c r="O30" s="33"/>
+      <c r="P30" s="33"/>
+      <c r="Q30" s="33"/>
     </row>
     <row r="31" spans="2:17" ht="15" customHeight="1">
-      <c r="B31" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="C31" s="38">
+      <c r="B31" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="24">
         <v>200000</v>
       </c>
-      <c r="D31" s="38">
+      <c r="D31" s="24">
         <v>150000</v>
       </c>
-      <c r="E31" s="38">
+      <c r="E31" s="24">
         <v>59500</v>
       </c>
-      <c r="F31" s="38">
+      <c r="F31" s="24">
         <v>59500</v>
       </c>
-      <c r="G31" s="41">
-        <f>SUM(C31:F31)</f>
+      <c r="G31" s="27">
+        <f t="shared" si="5"/>
         <v>469000</v>
       </c>
     </row>
     <row r="32" spans="2:17" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B32" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="31">
+      <c r="B32" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="19">
         <v>200000</v>
       </c>
-      <c r="D32" s="31">
+      <c r="D32" s="19">
         <v>150000</v>
       </c>
-      <c r="E32" s="31">
+      <c r="E32" s="19">
         <v>59500</v>
       </c>
-      <c r="F32" s="31">
+      <c r="F32" s="19">
         <v>59500</v>
       </c>
-      <c r="G32" s="32">
-        <f>SUM(C32:F32)</f>
+      <c r="G32" s="20">
+        <f t="shared" si="5"/>
         <v>469000</v>
       </c>
     </row>
     <row r="33" spans="2:7" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B33" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="31">
+      <c r="B33" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="19">
         <v>0</v>
       </c>
-      <c r="D33" s="31">
+      <c r="D33" s="19">
         <v>0</v>
       </c>
-      <c r="E33" s="31">
+      <c r="E33" s="19">
         <v>0</v>
       </c>
-      <c r="F33" s="31">
+      <c r="F33" s="19">
         <v>0</v>
       </c>
-      <c r="G33" s="32">
-        <f>SUM(C33:F33)</f>
+      <c r="G33" s="20">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:7" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B34" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="31">
+      <c r="B34" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="19">
         <v>0</v>
       </c>
-      <c r="D34" s="31">
+      <c r="D34" s="19">
         <v>0</v>
       </c>
-      <c r="E34" s="31">
+      <c r="E34" s="19">
         <v>0</v>
       </c>
-      <c r="F34" s="31">
+      <c r="F34" s="19">
         <v>0</v>
       </c>
-      <c r="G34" s="32">
-        <f>SUM(C34:F34)</f>
+      <c r="G34" s="20">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:7" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B35" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="31">
+      <c r="B35" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="19">
         <v>0</v>
       </c>
-      <c r="D35" s="31">
+      <c r="D35" s="19">
         <v>0</v>
       </c>
-      <c r="E35" s="31">
+      <c r="E35" s="19">
         <v>0</v>
       </c>
-      <c r="F35" s="31">
+      <c r="F35" s="19">
         <v>0</v>
       </c>
-      <c r="G35" s="32">
-        <f>SUM(C35:F35)</f>
+      <c r="G35" s="20">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:7" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B36" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="31">
+      <c r="B36" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="19">
         <v>0</v>
       </c>
-      <c r="D36" s="31">
+      <c r="D36" s="19">
         <v>0</v>
       </c>
-      <c r="E36" s="31">
+      <c r="E36" s="19">
         <v>0</v>
       </c>
-      <c r="F36" s="31">
+      <c r="F36" s="19">
         <v>0</v>
       </c>
-      <c r="G36" s="32">
-        <f>SUM(C36:F36)</f>
+      <c r="G36" s="20">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="2:7" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B37" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="31"/>
-      <c r="G37" s="32">
-        <f>SUM(C37:F37)</f>
+      <c r="B37" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="20">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="15" customHeight="1">
-      <c r="B38" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" s="53">
+      <c r="B38" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="35">
         <v>92000</v>
       </c>
-      <c r="D38" s="53">
+      <c r="D38" s="35">
         <v>47000</v>
       </c>
-      <c r="E38" s="53">
+      <c r="E38" s="35">
         <v>47000</v>
       </c>
-      <c r="F38" s="53">
+      <c r="F38" s="35">
         <v>92000</v>
       </c>
-      <c r="G38" s="54">
-        <f>SUM(C38:F38)</f>
+      <c r="G38" s="36">
+        <f t="shared" si="5"/>
         <v>278000</v>
       </c>
     </row>
     <row r="39" spans="2:7" ht="15" customHeight="1">
-      <c r="B39" s="55" t="s">
-        <v>17</v>
-      </c>
-      <c r="C39" s="58">
+      <c r="B39" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" s="38">
         <v>7519.1853693420235</v>
       </c>
-      <c r="D39" s="58">
+      <c r="D39" s="38">
         <v>6641.9617369629505</v>
       </c>
-      <c r="E39" s="58">
+      <c r="E39" s="38">
         <v>7373.6848565071314</v>
       </c>
-      <c r="F39" s="58">
+      <c r="F39" s="38">
         <v>8877.6340335841178</v>
       </c>
-      <c r="G39" s="59">
-        <f>SUM(C39:F39)</f>
+      <c r="G39" s="39">
+        <f t="shared" si="5"/>
         <v>30412.465996396226</v>
       </c>
     </row>
     <row r="40" spans="2:7" ht="15" customHeight="1">
-      <c r="B40" s="60" t="s">
-        <v>18</v>
-      </c>
-      <c r="C40" s="63">
-        <f t="shared" ref="C40:G40" si="4">IFERROR(((C7+C15)-(C23+C31))/(C7+C15),0)</f>
+      <c r="B40" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" s="42">
+        <f t="shared" ref="C40:G40" si="6">IFERROR(((C7+C15)-(C23+C31))/(C7+C15),0)</f>
         <v>0.40064579873320255</v>
       </c>
-      <c r="D40" s="63">
-        <f t="shared" si="4"/>
+      <c r="D40" s="42">
+        <f t="shared" si="6"/>
         <v>0.40526685128718881</v>
       </c>
-      <c r="E40" s="63">
-        <f t="shared" si="4"/>
+      <c r="E40" s="42">
+        <f t="shared" si="6"/>
         <v>0.42725926237307682</v>
       </c>
-      <c r="F40" s="63">
-        <f t="shared" si="4"/>
+      <c r="F40" s="42">
+        <f t="shared" si="6"/>
         <v>0.42727248824054043</v>
       </c>
-      <c r="G40" s="61">
-        <f t="shared" si="4"/>
+      <c r="G40" s="41">
+        <f t="shared" si="6"/>
         <v>0.4177412717066028</v>
       </c>
     </row>
     <row r="41" spans="2:7" ht="15" customHeight="1">
-      <c r="B41" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="C41" s="47">
-        <f t="shared" ref="C41:G41" si="5">SUM(C42:C44)</f>
+      <c r="B41" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C41" s="31">
+        <f t="shared" ref="C41:G41" si="7">SUM(C42:C44)</f>
         <v>889790.92769528122</v>
       </c>
-      <c r="D41" s="47">
-        <f t="shared" si="5"/>
+      <c r="D41" s="31">
+        <f t="shared" si="7"/>
         <v>768149.36442099395</v>
       </c>
-      <c r="E41" s="47">
-        <f t="shared" si="5"/>
+      <c r="E41" s="31">
+        <f t="shared" si="7"/>
         <v>1293104.1267819151</v>
       </c>
-      <c r="F41" s="47">
-        <f t="shared" si="5"/>
+      <c r="F41" s="31">
+        <f t="shared" si="7"/>
         <v>1293181.2784371357</v>
       </c>
-      <c r="G41" s="48">
-        <f t="shared" si="5"/>
+      <c r="G41" s="32">
+        <f t="shared" si="7"/>
         <v>4244225.6973353261</v>
       </c>
     </row>
     <row r="42" spans="2:7" ht="15" customHeight="1">
-      <c r="B42" s="64" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="67">
+      <c r="B42" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" s="44">
         <v>787608.09750660195</v>
       </c>
-      <c r="D42" s="67">
+      <c r="D42" s="44">
         <v>691518.04366627696</v>
       </c>
-      <c r="E42" s="67">
+      <c r="E42" s="44">
         <v>1262702.2399894623</v>
       </c>
-      <c r="F42" s="67">
+      <c r="F42" s="44">
         <v>1262779.391644683</v>
       </c>
-      <c r="G42" s="68">
+      <c r="G42" s="45">
         <f>SUM(C42:F42)</f>
         <v>4004607.7728070244</v>
       </c>
     </row>
     <row r="43" spans="2:7" ht="15" customHeight="1">
-      <c r="B43" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="C43" s="53">
+      <c r="B43" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="35">
         <v>102182.83018867925</v>
       </c>
-      <c r="D43" s="53">
+      <c r="D43" s="35">
         <v>76631.320754716988</v>
       </c>
-      <c r="E43" s="53">
+      <c r="E43" s="35">
         <v>30401.886792452831</v>
       </c>
-      <c r="F43" s="53">
+      <c r="F43" s="35">
         <v>30401.886792452831</v>
       </c>
-      <c r="G43" s="54">
+      <c r="G43" s="36">
         <f>SUM(C43:F43)</f>
         <v>239617.9245283019</v>
       </c>
     </row>
     <row r="44" spans="2:7" ht="15" customHeight="1">
-      <c r="B44" s="55" t="s">
-        <v>17</v>
-      </c>
-      <c r="C44" s="58">
+      <c r="B44" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" s="38">
         <v>0</v>
       </c>
-      <c r="D44" s="58">
+      <c r="D44" s="38">
         <v>0</v>
       </c>
-      <c r="E44" s="58">
+      <c r="E44" s="38">
         <v>0</v>
       </c>
-      <c r="F44" s="58">
+      <c r="F44" s="38">
         <v>0</v>
       </c>
-      <c r="G44" s="59">
+      <c r="G44" s="39">
         <f>SUM(C44:F44)</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="2:7" ht="15" customHeight="1">
-      <c r="B45" s="60" t="s">
-        <v>21</v>
-      </c>
-      <c r="C45" s="71">
-        <f t="shared" ref="C45:G45" si="6">IFERROR((C15+C7)/(C42+C43),0)</f>
+      <c r="B45" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" s="46">
+        <f t="shared" ref="C45:G45" si="8">IFERROR((C15+C7)/(C42+C43),0)</f>
         <v>4.9791104214090263</v>
       </c>
-      <c r="D45" s="71">
-        <f t="shared" si="6"/>
+      <c r="D45" s="46">
+        <f t="shared" si="8"/>
         <v>4.9838253743171705</v>
       </c>
-      <c r="E45" s="71">
-        <f t="shared" si="6"/>
+      <c r="E45" s="46">
+        <f t="shared" si="8"/>
         <v>5.0134006295858962</v>
       </c>
-      <c r="F45" s="71">
-        <f t="shared" si="6"/>
+      <c r="F45" s="46">
+        <f t="shared" si="8"/>
         <v>5.0132793072873794</v>
       </c>
-      <c r="G45" s="72">
-        <f t="shared" si="6"/>
+      <c r="G45" s="47">
+        <f t="shared" si="8"/>
         <v>5.0008220757544075</v>
       </c>
     </row>
     <row r="46" spans="2:7" ht="15" customHeight="1">
-      <c r="B46" s="73" t="s">
-        <v>22</v>
-      </c>
-      <c r="C46" s="76">
-        <f t="shared" ref="C46:F46" si="7">C22-C41</f>
+      <c r="B46" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" s="49">
+        <f t="shared" ref="C46:F46" si="9">C22-C41</f>
         <v>1865087.500674061</v>
       </c>
-      <c r="D46" s="76">
-        <f t="shared" si="7"/>
+      <c r="D46" s="49">
+        <f t="shared" si="9"/>
         <v>1562322.7693159699</v>
       </c>
-      <c r="E46" s="76">
-        <f t="shared" si="7"/>
+      <c r="E46" s="49">
+        <f t="shared" si="9"/>
         <v>2474261.3010745924</v>
       </c>
-      <c r="F46" s="76">
-        <f t="shared" si="7"/>
+      <c r="F46" s="49">
+        <f t="shared" si="9"/>
         <v>2520734.0275964485</v>
       </c>
-      <c r="G46" s="77">
+      <c r="G46" s="50">
         <f>SUM(C46:F46)</f>
         <v>8422405.5986610726</v>
       </c>
     </row>
     <row r="47" spans="2:7" ht="15" customHeight="1">
-      <c r="B47" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="C47" s="81">
-        <f t="shared" ref="C47:G47" si="8">IFERROR(C46/C$22,0)</f>
+      <c r="B47" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47" s="53">
+        <f t="shared" ref="C47:G47" si="10">IFERROR(C46/C$22,0)</f>
         <v>0.67701263383082821</v>
       </c>
-      <c r="D47" s="81">
-        <f t="shared" si="8"/>
+      <c r="D47" s="53">
+        <f t="shared" si="10"/>
         <v>0.67038895110526409</v>
       </c>
-      <c r="E47" s="81">
-        <f t="shared" si="8"/>
+      <c r="E47" s="53">
+        <f t="shared" si="10"/>
         <v>0.65676169420133912</v>
       </c>
-      <c r="F47" s="81">
-        <f t="shared" si="8"/>
+      <c r="F47" s="53">
+        <f t="shared" si="10"/>
         <v>0.66093078249762571</v>
       </c>
-      <c r="G47" s="79">
-        <f t="shared" si="8"/>
+      <c r="G47" s="52">
+        <f t="shared" si="10"/>
         <v>0.66492861454988295</v>
       </c>
     </row>
     <row r="48" spans="2:7" ht="15" customHeight="1">
-      <c r="B48" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="47">
-        <f t="shared" ref="C48:G48" si="9">SUM(C49:C53)</f>
+      <c r="B48" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" s="31">
+        <f t="shared" ref="C48:G48" si="11">SUM(C49:C53)</f>
         <v>972614.67230980424</v>
       </c>
-      <c r="D48" s="47">
-        <f t="shared" si="9"/>
+      <c r="D48" s="31">
+        <f t="shared" si="11"/>
         <v>861243.33385203825</v>
       </c>
-      <c r="E48" s="47">
-        <f t="shared" si="9"/>
+      <c r="E48" s="31">
+        <f t="shared" si="11"/>
         <v>1176274.9464831592</v>
       </c>
-      <c r="F48" s="47">
-        <f t="shared" si="9"/>
+      <c r="F48" s="31">
+        <f t="shared" si="11"/>
         <v>1323300.2754963848</v>
       </c>
-      <c r="G48" s="48">
-        <f t="shared" si="9"/>
+      <c r="G48" s="32">
+        <f t="shared" si="11"/>
         <v>4333433.2281413861</v>
       </c>
     </row>
     <row r="49" spans="2:7" ht="15" customHeight="1">
-      <c r="B49" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="C49" s="67">
+      <c r="B49" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C49" s="44">
         <v>450990.37800932431</v>
       </c>
-      <c r="D49" s="67">
+      <c r="D49" s="44">
         <v>390647.49729248328</v>
       </c>
-      <c r="E49" s="67">
+      <c r="E49" s="44">
         <v>671058.47216733126</v>
       </c>
-      <c r="F49" s="67">
+      <c r="F49" s="44">
         <v>671066.90821885027</v>
       </c>
-      <c r="G49" s="68">
+      <c r="G49" s="45">
         <f>SUM(C49:F49)</f>
         <v>2183763.2556879893</v>
       </c>
     </row>
     <row r="50" spans="2:7" ht="15" customHeight="1">
-      <c r="B50" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="C50" s="53">
+      <c r="B50" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="35">
         <v>166730.38378890732</v>
       </c>
-      <c r="D50" s="53">
+      <c r="D50" s="35">
         <v>154891.46136444801</v>
       </c>
-      <c r="E50" s="53">
+      <c r="E50" s="35">
         <v>100979.79448093731</v>
       </c>
-      <c r="F50" s="53">
+      <c r="F50" s="35">
         <v>216151.26244589413</v>
       </c>
-      <c r="G50" s="54">
+      <c r="G50" s="36">
         <f>SUM(C50:F50)</f>
         <v>638752.90208018676</v>
       </c>
     </row>
     <row r="51" spans="2:7" ht="15" customHeight="1">
-      <c r="B51" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="C51" s="53">
+      <c r="B51" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51" s="35">
         <v>134489.20025142346</v>
       </c>
-      <c r="D51" s="53">
+      <c r="D51" s="35">
         <v>121009.03041288056</v>
       </c>
-      <c r="E51" s="53">
+      <c r="E51" s="35">
         <v>99756.373265602931</v>
       </c>
-      <c r="F51" s="53">
+      <c r="F51" s="35">
         <v>131598.41374620117</v>
       </c>
-      <c r="G51" s="54">
+      <c r="G51" s="36">
         <f>SUM(C51:F51)</f>
         <v>486853.01767610817</v>
       </c>
     </row>
     <row r="52" spans="2:7" ht="15" customHeight="1">
-      <c r="B52" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="C52" s="53">
+      <c r="B52" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C52" s="35">
         <v>220404.71026014912</v>
       </c>
-      <c r="D52" s="53">
+      <c r="D52" s="35">
         <v>194695.34478222634</v>
       </c>
-      <c r="E52" s="53">
+      <c r="E52" s="35">
         <v>304480.30656928773</v>
       </c>
-      <c r="F52" s="53">
+      <c r="F52" s="35">
         <v>304483.69108543918</v>
       </c>
-      <c r="G52" s="54">
+      <c r="G52" s="36">
         <f>SUM(C52:F52)</f>
         <v>1024064.0526971023</v>
       </c>
     </row>
     <row r="53" spans="2:7" ht="15" customHeight="1">
-      <c r="B53" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="C53" s="53">
+      <c r="B53" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" s="35">
         <v>0</v>
       </c>
-      <c r="D53" s="53">
+      <c r="D53" s="35">
         <v>0</v>
       </c>
-      <c r="E53" s="53">
+      <c r="E53" s="35">
         <v>0</v>
       </c>
-      <c r="F53" s="53">
+      <c r="F53" s="35">
         <v>0</v>
       </c>
-      <c r="G53" s="54">
+      <c r="G53" s="36">
         <f>SUM(C53:F53)</f>
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="2:7" ht="15" customHeight="1">
-      <c r="B54" s="73" t="s">
-        <v>29</v>
-      </c>
-      <c r="C54" s="76">
-        <f t="shared" ref="C54:G54" si="10">C46-C48</f>
+      <c r="B54" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="C54" s="49">
+        <f t="shared" ref="C54:G54" si="12">C46-C48</f>
         <v>892472.82836425677</v>
       </c>
-      <c r="D54" s="76">
-        <f t="shared" si="10"/>
+      <c r="D54" s="49">
+        <f t="shared" si="12"/>
         <v>701079.43546393164</v>
       </c>
-      <c r="E54" s="76">
-        <f t="shared" si="10"/>
+      <c r="E54" s="49">
+        <f t="shared" si="12"/>
         <v>1297986.3545914332</v>
       </c>
-      <c r="F54" s="76">
-        <f t="shared" si="10"/>
+      <c r="F54" s="49">
+        <f t="shared" si="12"/>
         <v>1197433.7521000637</v>
       </c>
-      <c r="G54" s="77">
-        <f t="shared" si="10"/>
+      <c r="G54" s="50">
+        <f t="shared" si="12"/>
         <v>4088972.3705196865</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="15" customHeight="1">
-      <c r="B55" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="C55" s="81">
-        <f t="shared" ref="C55:G55" si="11">IFERROR(C54/C$22,0)</f>
+      <c r="B55" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55" s="53">
+        <f t="shared" ref="C55:G55" si="13">IFERROR(C54/C$22,0)</f>
         <v>0.32396087579535265</v>
       </c>
-      <c r="D55" s="81">
-        <f t="shared" si="11"/>
+      <c r="D55" s="53">
+        <f t="shared" si="13"/>
         <v>0.30083150333135938</v>
       </c>
-      <c r="E55" s="81">
-        <f t="shared" si="11"/>
+      <c r="E55" s="53">
+        <f t="shared" si="13"/>
         <v>0.34453423206411377</v>
       </c>
-      <c r="F55" s="81">
-        <f t="shared" si="11"/>
+      <c r="F55" s="53">
+        <f t="shared" si="13"/>
         <v>0.31396443182829281</v>
       </c>
-      <c r="G55" s="79">
-        <f t="shared" si="11"/>
+      <c r="G55" s="52">
+        <f t="shared" si="13"/>
         <v>0.3228145096330472</v>
       </c>
     </row>
     <row r="56" spans="2:7" ht="15" customHeight="1">
-      <c r="B56" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="C56" s="47">
-        <f t="shared" ref="C56:G56" si="12">SUM(C57:C64)</f>
+      <c r="B56" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="C56" s="31">
+        <f t="shared" ref="C56:G56" si="14">SUM(C57:C64)</f>
         <v>496594.79709480423</v>
       </c>
-      <c r="D56" s="47">
-        <f t="shared" si="12"/>
+      <c r="D56" s="31">
+        <f t="shared" si="14"/>
         <v>629262.15039746102</v>
       </c>
-      <c r="E56" s="47">
-        <f t="shared" si="12"/>
+      <c r="E56" s="31">
+        <f t="shared" si="14"/>
         <v>543890.37136525079</v>
       </c>
-      <c r="F56" s="47">
-        <f t="shared" si="12"/>
+      <c r="F56" s="31">
+        <f t="shared" si="14"/>
         <v>559880.00338142994</v>
       </c>
-      <c r="G56" s="48">
-        <f t="shared" si="12"/>
+      <c r="G56" s="32">
+        <f t="shared" si="14"/>
         <v>2229627.3222389459</v>
       </c>
     </row>
     <row r="57" spans="2:7" ht="15" customHeight="1">
-      <c r="B57" s="64" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="67">
+      <c r="B57" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="C57" s="44">
         <v>339985.07520833332</v>
       </c>
-      <c r="D57" s="67">
+      <c r="D57" s="44">
         <v>339985.07520833332</v>
       </c>
-      <c r="E57" s="67">
+      <c r="E57" s="44">
         <v>339985.07520833332</v>
       </c>
-      <c r="F57" s="67">
+      <c r="F57" s="44">
         <v>342785.07520833332</v>
       </c>
-      <c r="G57" s="68">
-        <f>SUM(C57:F57)</f>
+      <c r="G57" s="45">
+        <f t="shared" ref="G57:G64" si="15">SUM(C57:F57)</f>
         <v>1362740.3008333333</v>
       </c>
     </row>
     <row r="58" spans="2:7" ht="15" customHeight="1">
-      <c r="B58" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="C58" s="53">
+      <c r="B58" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C58" s="35">
         <v>19166.666666666672</v>
       </c>
-      <c r="D58" s="53">
+      <c r="D58" s="35">
         <v>101166.66666666667</v>
       </c>
-      <c r="E58" s="53">
+      <c r="E58" s="35">
         <v>54166.666666666672</v>
       </c>
-      <c r="F58" s="53">
+      <c r="F58" s="35">
         <v>72166.666666666672</v>
       </c>
-      <c r="G58" s="54">
-        <f>SUM(C58:F58)</f>
+      <c r="G58" s="36">
+        <f t="shared" si="15"/>
         <v>246666.66666666669</v>
       </c>
     </row>
     <row r="59" spans="2:7" ht="15" customHeight="1">
-      <c r="B59" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="C59" s="53">
+      <c r="B59" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="35">
         <v>2150</v>
       </c>
-      <c r="D59" s="53">
+      <c r="D59" s="35">
         <v>1950</v>
       </c>
-      <c r="E59" s="53">
+      <c r="E59" s="35">
         <v>1450</v>
       </c>
-      <c r="F59" s="53">
+      <c r="F59" s="35">
         <v>6150</v>
       </c>
-      <c r="G59" s="54">
-        <f>SUM(C59:F59)</f>
+      <c r="G59" s="36">
+        <f t="shared" si="15"/>
         <v>11700</v>
       </c>
     </row>
     <row r="60" spans="2:7" ht="15" customHeight="1">
-      <c r="B60" s="50" t="s">
-        <v>34</v>
-      </c>
-      <c r="C60" s="53">
+      <c r="B60" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C60" s="35">
         <v>24658.39</v>
       </c>
-      <c r="D60" s="53">
+      <c r="D60" s="35">
         <v>24658.39</v>
       </c>
-      <c r="E60" s="53">
+      <c r="E60" s="35">
         <v>24658.39</v>
       </c>
-      <c r="F60" s="53">
+      <c r="F60" s="35">
         <v>24658.39</v>
       </c>
-      <c r="G60" s="54">
-        <f>SUM(C60:F60)</f>
+      <c r="G60" s="36">
+        <f t="shared" si="15"/>
         <v>98633.56</v>
       </c>
     </row>
     <row r="61" spans="2:7" ht="15" customHeight="1">
-      <c r="B61" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="C61" s="53">
+      <c r="B61" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="C61" s="35">
         <v>2000</v>
       </c>
-      <c r="D61" s="53">
+      <c r="D61" s="35">
         <v>37500</v>
       </c>
-      <c r="E61" s="53">
+      <c r="E61" s="35">
         <v>4500</v>
       </c>
-      <c r="F61" s="53">
+      <c r="F61" s="35">
         <v>2000</v>
       </c>
-      <c r="G61" s="54">
-        <f>SUM(C61:F61)</f>
+      <c r="G61" s="36">
+        <f t="shared" si="15"/>
         <v>46000</v>
       </c>
     </row>
     <row r="62" spans="2:7" ht="15" customHeight="1">
-      <c r="B62" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="C62" s="53">
+      <c r="B62" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C62" s="35">
         <v>87943.185219804174</v>
       </c>
-      <c r="D62" s="53">
+      <c r="D62" s="35">
         <v>102160.53852246104</v>
       </c>
-      <c r="E62" s="53">
+      <c r="E62" s="35">
         <v>98388.759490250755</v>
       </c>
-      <c r="F62" s="53">
+      <c r="F62" s="35">
         <v>90028.391506429951</v>
       </c>
-      <c r="G62" s="54">
-        <f>SUM(C62:F62)</f>
+      <c r="G62" s="36">
+        <f t="shared" si="15"/>
         <v>378520.87473894592</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="15" customHeight="1">
-      <c r="B63" s="50" t="s">
-        <v>36</v>
-      </c>
-      <c r="C63" s="53">
+      <c r="B63" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C63" s="35">
         <v>4022.2</v>
       </c>
-      <c r="D63" s="53">
+      <c r="D63" s="35">
         <v>4022.2</v>
       </c>
-      <c r="E63" s="53">
+      <c r="E63" s="35">
         <v>4022.2</v>
       </c>
-      <c r="F63" s="53">
+      <c r="F63" s="35">
         <v>4022.2</v>
       </c>
-      <c r="G63" s="54">
-        <f>SUM(C63:F63)</f>
+      <c r="G63" s="36">
+        <f t="shared" si="15"/>
         <v>16088.8</v>
       </c>
     </row>
     <row r="64" spans="2:7" ht="15" customHeight="1">
-      <c r="B64" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="C64" s="53">
+      <c r="B64" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="C64" s="35">
         <v>16669.28</v>
       </c>
-      <c r="D64" s="53">
+      <c r="D64" s="35">
         <v>17819.280000000002</v>
       </c>
-      <c r="E64" s="53">
+      <c r="E64" s="35">
         <v>16719.28</v>
       </c>
-      <c r="F64" s="53">
+      <c r="F64" s="35">
         <v>18069.280000000002</v>
       </c>
-      <c r="G64" s="54">
-        <f>SUM(C64:F64)</f>
+      <c r="G64" s="36">
+        <f t="shared" si="15"/>
         <v>69277.119999999995</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="15" customHeight="1">
-      <c r="B65" s="73" t="s">
-        <v>37</v>
-      </c>
-      <c r="C65" s="76">
-        <f t="shared" ref="C65:G65" si="13">C54-C56</f>
+      <c r="B65" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="C65" s="49">
+        <f t="shared" ref="C65:G65" si="16">C54-C56</f>
         <v>395878.03126945253</v>
       </c>
-      <c r="D65" s="76">
-        <f t="shared" si="13"/>
+      <c r="D65" s="49">
+        <f t="shared" si="16"/>
         <v>71817.28506647062</v>
       </c>
-      <c r="E65" s="76">
-        <f t="shared" si="13"/>
+      <c r="E65" s="49">
+        <f t="shared" si="16"/>
         <v>754095.9832261824</v>
       </c>
-      <c r="F65" s="76">
-        <f t="shared" si="13"/>
+      <c r="F65" s="49">
+        <f t="shared" si="16"/>
         <v>637553.74871863378</v>
       </c>
-      <c r="G65" s="77">
-        <f t="shared" si="13"/>
+      <c r="G65" s="50">
+        <f t="shared" si="16"/>
         <v>1859345.0482807406</v>
       </c>
     </row>
     <row r="66" spans="2:7" ht="15" customHeight="1">
-      <c r="B66" s="82" t="s">
-        <v>23</v>
-      </c>
-      <c r="C66" s="85">
-        <f t="shared" ref="C66:G66" si="14">IFERROR(C65/C$22,0)</f>
+      <c r="B66" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="C66" s="56">
+        <f t="shared" ref="C66:G66" si="17">IFERROR(C65/C$22,0)</f>
         <v>0.14370072638877907</v>
       </c>
-      <c r="D66" s="85">
-        <f t="shared" si="14"/>
+      <c r="D66" s="56">
+        <f t="shared" si="17"/>
         <v>3.0816624677382436E-2</v>
       </c>
-      <c r="E66" s="85">
-        <f t="shared" si="14"/>
+      <c r="E66" s="56">
+        <f t="shared" si="17"/>
         <v>0.20016534038622194</v>
       </c>
-      <c r="F66" s="85">
-        <f t="shared" si="14"/>
+      <c r="F66" s="56">
+        <f t="shared" si="17"/>
         <v>0.1671651564233817</v>
       </c>
-      <c r="G66" s="83">
-        <f t="shared" si="14"/>
+      <c r="G66" s="55">
+        <f t="shared" si="17"/>
         <v>0.14679080845026513</v>
       </c>
     </row>
-    <row r="67" spans="2:7" ht="15" hidden="1" customHeight="1">
-      <c r="B67" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="C67" s="86">
-        <f t="shared" ref="C67:G67" si="15">SUM(C68:C75)</f>
-        <v>194845.24380144037</v>
-      </c>
-      <c r="D67" s="86">
-        <f t="shared" si="15"/>
-        <v>177868.99201614523</v>
-      </c>
-      <c r="E67" s="86">
-        <f t="shared" si="15"/>
-        <v>235344.72378092696</v>
-      </c>
-      <c r="F67" s="87">
-        <f t="shared" si="15"/>
-        <v>237206.71890801005</v>
-      </c>
-      <c r="G67" s="45">
-        <f t="shared" si="15"/>
-        <v>845265.67850652267</v>
-      </c>
-    </row>
-    <row r="68" spans="2:7" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="B68" s="64" t="s">
-        <v>39</v>
-      </c>
-      <c r="C68" s="88">
-        <v>76666.666666666672</v>
-      </c>
-      <c r="D68" s="88">
-        <v>76666.666666666672</v>
-      </c>
-      <c r="E68" s="88">
-        <v>76666.666666666672</v>
-      </c>
-      <c r="F68" s="89">
-        <v>76666.666666666672</v>
-      </c>
-      <c r="G68" s="65">
-        <f>SUM(C68:F68)</f>
-        <v>306666.66666666669</v>
-      </c>
-    </row>
-    <row r="69" spans="2:7" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="B69" s="50" t="s">
-        <v>40</v>
-      </c>
-      <c r="C69" s="90">
-        <v>0</v>
-      </c>
-      <c r="D69" s="90">
-        <v>0</v>
-      </c>
-      <c r="E69" s="90">
-        <v>0</v>
-      </c>
-      <c r="F69" s="91">
-        <v>0</v>
-      </c>
-      <c r="G69" s="51">
-        <f>SUM(C69:F69)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="2:7" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="B70" s="50" t="s">
-        <v>41</v>
-      </c>
-      <c r="C70" s="90">
-        <v>0</v>
-      </c>
-      <c r="D70" s="90">
-        <v>0</v>
-      </c>
-      <c r="E70" s="90">
-        <v>0</v>
-      </c>
-      <c r="F70" s="91">
-        <v>0</v>
-      </c>
-      <c r="G70" s="51">
-        <f>SUM(C70:F70)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:7" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="B71" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="C71" s="90">
-        <v>0</v>
-      </c>
-      <c r="D71" s="90">
-        <v>0</v>
-      </c>
-      <c r="E71" s="90">
-        <v>0</v>
-      </c>
-      <c r="F71" s="91">
-        <v>0</v>
-      </c>
-      <c r="G71" s="51">
-        <f>SUM(C71:F71)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="2:7" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="B72" s="50" t="s">
-        <v>43</v>
-      </c>
-      <c r="C72" s="90">
-        <v>3000</v>
-      </c>
-      <c r="D72" s="90">
-        <v>3000</v>
-      </c>
-      <c r="E72" s="90">
-        <v>3000</v>
-      </c>
-      <c r="F72" s="91">
-        <v>3000</v>
-      </c>
-      <c r="G72" s="51">
-        <f>SUM(C72:F72)</f>
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="73" spans="2:7" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="B73" s="50" t="s">
-        <v>44</v>
-      </c>
-      <c r="C73" s="90">
-        <v>110195.1371347737</v>
-      </c>
-      <c r="D73" s="90">
-        <v>93218.885349478558</v>
-      </c>
-      <c r="E73" s="90">
-        <v>150694.6171142603</v>
-      </c>
-      <c r="F73" s="91">
-        <v>152556.61224134336</v>
-      </c>
-      <c r="G73" s="51">
-        <f>SUM(C73:F73)</f>
-        <v>506665.25183985592</v>
-      </c>
-    </row>
-    <row r="74" spans="2:7" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="B74" s="50" t="s">
-        <v>45</v>
-      </c>
-      <c r="C74" s="90">
-        <v>4983.4399999999996</v>
-      </c>
-      <c r="D74" s="90">
-        <v>4983.4399999999996</v>
-      </c>
-      <c r="E74" s="90">
-        <v>4983.4399999999996</v>
-      </c>
-      <c r="F74" s="91">
-        <v>4983.4399999999996</v>
-      </c>
-      <c r="G74" s="51">
-        <f>SUM(C74:F74)</f>
-        <v>19933.759999999998</v>
-      </c>
-    </row>
-    <row r="75" spans="2:7" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="B75" s="50" t="s">
-        <v>46</v>
-      </c>
-      <c r="C75" s="90">
-        <v>0</v>
-      </c>
-      <c r="D75" s="90">
-        <v>0</v>
-      </c>
-      <c r="E75" s="90">
-        <v>0</v>
-      </c>
-      <c r="F75" s="91">
-        <v>0</v>
-      </c>
-      <c r="G75" s="51">
-        <f>SUM(C75:F75)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="2:7" ht="15" hidden="1" customHeight="1" collapsed="1">
-      <c r="B76" s="73" t="s">
-        <v>47</v>
-      </c>
-      <c r="C76" s="92">
-        <f t="shared" ref="C76:G76" si="16">C65-C67</f>
-        <v>201032.78746801216</v>
-      </c>
-      <c r="D76" s="92">
-        <f t="shared" si="16"/>
-        <v>-106051.70694967461</v>
-      </c>
-      <c r="E76" s="92">
-        <f t="shared" si="16"/>
-        <v>518751.25944525545</v>
-      </c>
-      <c r="F76" s="93">
-        <f t="shared" si="16"/>
-        <v>400347.02981062373</v>
-      </c>
-      <c r="G76" s="74">
-        <f t="shared" si="16"/>
-        <v>1014079.369774218</v>
-      </c>
-    </row>
-    <row r="77" spans="2:7" ht="15" hidden="1" customHeight="1">
-      <c r="B77" s="82" t="s">
-        <v>23</v>
-      </c>
-      <c r="C77" s="95">
-        <f t="shared" ref="C77:G77" si="17">IFERROR(C76/C$22,0)</f>
-        <v>7.2973378933097521E-2</v>
-      </c>
-      <c r="D77" s="95">
-        <f t="shared" si="17"/>
-        <v>-4.5506532952882102E-2</v>
-      </c>
-      <c r="E77" s="95">
-        <f t="shared" si="17"/>
-        <v>0.13769602906304895</v>
-      </c>
-      <c r="F77" s="96">
-        <f t="shared" si="17"/>
-        <v>0.10497008918296583</v>
-      </c>
-      <c r="G77" s="94">
-        <f t="shared" si="17"/>
-        <v>8.0059121172552233E-2</v>
-      </c>
-    </row>
-    <row r="78" spans="2:7" collapsed="1"/>
+    <row r="67" spans="2:7" collapsed="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B4:B5"/>
@@ -18907,2320 +18372,1645 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="B1:S108"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="1"/>
+  <dimension ref="B1:Q83"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="2.75" style="1" customWidth="1"/>
     <col min="2" max="2" width="30.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.75" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="9" width="11.75" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11" style="1" customWidth="1"/>
-    <col min="11" max="12" width="9" style="1"/>
-    <col min="13" max="13" width="16.875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="9" style="1"/>
-    <col min="15" max="15" width="10.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="1"/>
+    <col min="3" max="7" width="11.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11" style="1" customWidth="1"/>
+    <col min="9" max="10" width="9" style="1"/>
+    <col min="11" max="11" width="16.875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9" style="1"/>
+    <col min="13" max="13" width="10.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" ht="9.9499999999999993" customHeight="1"/>
-    <row r="2" spans="2:19" ht="18" customHeight="1">
+    <row r="1" spans="2:17" ht="9.9499999999999993" customHeight="1"/>
+    <row r="2" spans="2:17" ht="18" customHeight="1">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
     </row>
-    <row r="3" spans="2:19" ht="9.9499999999999993" customHeight="1">
-      <c r="C3" s="5"/>
-      <c r="I3" s="5" t="s">
+    <row r="3" spans="2:17" ht="9.9499999999999993" customHeight="1">
+      <c r="G3" s="5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:19" ht="15" customHeight="1" thickBot="1">
-      <c r="B4" s="6" t="s">
+    <row r="4" spans="2:17" ht="15" customHeight="1" thickBot="1">
+      <c r="B4" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="10"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="7"/>
     </row>
-    <row r="5" spans="2:19" ht="15" customHeight="1">
-      <c r="B5" s="11"/>
-      <c r="C5" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="13">
-        <v>46023</v>
-      </c>
-      <c r="E5" s="97">
+    <row r="5" spans="2:17" ht="15" customHeight="1">
+      <c r="B5" s="68"/>
+      <c r="C5" s="57">
         <v>46266</v>
       </c>
-      <c r="F5" s="14">
-        <f t="shared" ref="F5:H5" si="0">EDATE(E5,1)</f>
+      <c r="D5" s="8">
+        <f t="shared" ref="D5:F5" si="0">EDATE(C5,1)</f>
         <v>46296</v>
       </c>
-      <c r="G5" s="14">
+      <c r="E5" s="8">
         <f t="shared" si="0"/>
         <v>46327</v>
       </c>
-      <c r="H5" s="14">
+      <c r="F5" s="8">
         <f t="shared" si="0"/>
         <v>46357</v>
       </c>
-      <c r="I5" s="15" t="s">
-        <v>48</v>
+      <c r="G5" s="9" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="6" spans="2:19" ht="15" customHeight="1">
-      <c r="B6" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="17">
-        <v>83274003</v>
-      </c>
-      <c r="D6" s="18">
-        <f t="shared" ref="D6:I6" si="1">SUM(D7,D15)</f>
-        <v>2535965</v>
-      </c>
-      <c r="E6" s="19">
-        <f t="shared" si="1"/>
+    <row r="6" spans="2:17" ht="15" customHeight="1">
+      <c r="B6" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="11">
+        <f t="shared" ref="C6:G6" si="1">SUM(C7,C15)</f>
         <v>3150867.7368170284</v>
       </c>
-      <c r="F6" s="19">
+      <c r="D6" s="11">
         <f t="shared" si="1"/>
         <v>3559319.5285416874</v>
       </c>
-      <c r="G6" s="19">
+      <c r="E6" s="11">
         <f t="shared" si="1"/>
         <v>7010159.5185636748</v>
       </c>
-      <c r="H6" s="19">
+      <c r="F6" s="11">
         <f t="shared" si="1"/>
         <v>6494858.7299860418</v>
       </c>
-      <c r="I6" s="20">
+      <c r="G6" s="12">
         <f t="shared" si="1"/>
-        <v>22751170.513908431</v>
+        <v>20215205.513908431</v>
       </c>
     </row>
-    <row r="7" spans="2:19" ht="15" customHeight="1">
-      <c r="B7" s="21" t="s">
+    <row r="7" spans="2:17" ht="15" customHeight="1">
+      <c r="B7" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="15">
+        <f>SUM(C8:C14)</f>
+        <v>2609298.7368170284</v>
+      </c>
+      <c r="D7" s="15">
+        <f>SUM(D8:D14)</f>
+        <v>3153173.5285416874</v>
+      </c>
+      <c r="E7" s="15">
+        <f>SUM(E8:E14)</f>
+        <v>6849029.5185636748</v>
+      </c>
+      <c r="F7" s="15">
+        <f>SUM(F8:F14)</f>
+        <v>6333728.7299860418</v>
+      </c>
+      <c r="G7" s="16">
+        <f t="shared" ref="G7:G21" si="2">SUM(C7:F7)</f>
+        <v>18945230.513908431</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" s="21" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B8" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="19">
+        <v>262474.012892753</v>
+      </c>
+      <c r="D8" s="19">
+        <v>433903.79921149899</v>
+      </c>
+      <c r="E8" s="19">
+        <v>2321150.7101700599</v>
+      </c>
+      <c r="F8" s="19">
+        <v>2744570.1181608802</v>
+      </c>
+      <c r="G8" s="20">
+        <f t="shared" si="2"/>
+        <v>5762098.6404351918</v>
+      </c>
+      <c r="H8" s="1"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+    </row>
+    <row r="9" spans="2:17" s="21" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B9" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="22">
-        <v>39538210</v>
-      </c>
-      <c r="D7" s="23">
-        <v>2515438</v>
-      </c>
-      <c r="E7" s="25">
-        <f>SUM(E8:E14)</f>
-        <v>2609298.7368170284</v>
-      </c>
-      <c r="F7" s="25">
-        <f>SUM(F8:F14)</f>
-        <v>3153173.5285416874</v>
-      </c>
-      <c r="G7" s="25">
-        <f>SUM(G8:G14)</f>
-        <v>6849029.5185636748</v>
-      </c>
-      <c r="H7" s="25">
-        <f>SUM(H8:H14)</f>
-        <v>6333728.7299860418</v>
-      </c>
-      <c r="I7" s="26">
-        <f>SUM(D7:H7)</f>
-        <v>21460668.513908431</v>
-      </c>
+      <c r="C9" s="19">
+        <v>955462.17630225001</v>
+      </c>
+      <c r="D9" s="19">
+        <v>1090250.08894486</v>
+      </c>
+      <c r="E9" s="19">
+        <v>2080627.0666813899</v>
+      </c>
+      <c r="F9" s="19">
+        <v>1296753.8522276301</v>
+      </c>
+      <c r="G9" s="20">
+        <f t="shared" si="2"/>
+        <v>5423093.1841561301</v>
+      </c>
+      <c r="H9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
     </row>
-    <row r="8" spans="2:19" s="33" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B8" s="28" t="s">
+    <row r="10" spans="2:17" s="21" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B10" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C10" s="19">
+        <v>871576.75637146505</v>
+      </c>
+      <c r="D10" s="19">
+        <v>990068.89531308005</v>
+      </c>
+      <c r="E10" s="19">
+        <v>1737122.4204106899</v>
+      </c>
+      <c r="F10" s="19">
+        <v>1564212.05660536</v>
+      </c>
+      <c r="G10" s="20">
+        <f t="shared" si="2"/>
+        <v>5162980.1287005953</v>
+      </c>
+      <c r="H10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+    </row>
+    <row r="11" spans="2:17" s="21" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B11" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="19">
+        <v>410740.85847973399</v>
+      </c>
+      <c r="D11" s="19">
+        <v>519223.106757553</v>
+      </c>
+      <c r="E11" s="19">
+        <v>329478.02922197402</v>
+      </c>
+      <c r="F11" s="19">
+        <v>228707.318852753</v>
+      </c>
+      <c r="G11" s="20">
+        <f t="shared" si="2"/>
+        <v>1488149.3133120139</v>
+      </c>
+      <c r="H11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+    </row>
+    <row r="12" spans="2:17" s="21" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B12" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="19">
+        <v>55694.6124072233</v>
+      </c>
+      <c r="D12" s="19">
+        <v>63247.722184106402</v>
+      </c>
+      <c r="E12" s="19">
+        <v>109498.235406874</v>
+      </c>
+      <c r="F12" s="19">
+        <v>100261.487526592</v>
+      </c>
+      <c r="G12" s="20">
+        <f t="shared" si="2"/>
+        <v>328702.0575247957</v>
+      </c>
+      <c r="H12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+    </row>
+    <row r="13" spans="2:17" s="21" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B13" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="19">
+        <v>53350.320363603103</v>
+      </c>
+      <c r="D13" s="19">
+        <v>56479.916130589401</v>
+      </c>
+      <c r="E13" s="19">
+        <v>271153.056672687</v>
+      </c>
+      <c r="F13" s="19">
+        <v>399223.89661282598</v>
+      </c>
+      <c r="G13" s="20">
+        <f t="shared" si="2"/>
+        <v>780207.18977970548</v>
+      </c>
+      <c r="H13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+    </row>
+    <row r="14" spans="2:17" s="21" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B14" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="20">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D8" s="30">
+      <c r="H14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+    </row>
+    <row r="15" spans="2:17" ht="15" customHeight="1">
+      <c r="B15" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="25">
+        <v>541569</v>
+      </c>
+      <c r="D15" s="25">
+        <v>406146</v>
+      </c>
+      <c r="E15" s="25">
+        <v>161130</v>
+      </c>
+      <c r="F15" s="26">
+        <v>161130</v>
+      </c>
+      <c r="G15" s="27">
+        <f t="shared" si="2"/>
+        <v>1269975</v>
+      </c>
+      <c r="I15" s="28"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="28"/>
+      <c r="Q15" s="28"/>
+    </row>
+    <row r="16" spans="2:17" s="21" customFormat="1" ht="15" customHeight="1" outlineLevel="2">
+      <c r="B16" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="19">
+        <f>C15</f>
+        <v>541569</v>
+      </c>
+      <c r="D16" s="19">
+        <f>D15</f>
+        <v>406146</v>
+      </c>
+      <c r="E16" s="19">
+        <f>E15</f>
+        <v>161130</v>
+      </c>
+      <c r="F16" s="19">
+        <f>F15</f>
+        <v>161130</v>
+      </c>
+      <c r="G16" s="20">
+        <f t="shared" si="2"/>
+        <v>1269975</v>
+      </c>
+      <c r="H16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+    </row>
+    <row r="17" spans="2:17" s="21" customFormat="1" ht="15" customHeight="1" outlineLevel="2">
+      <c r="B17" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="E8" s="31">
-        <v>262474.012892753</v>
-      </c>
-      <c r="F8" s="31">
-        <v>433903.79921149899</v>
-      </c>
-      <c r="G8" s="31">
-        <v>2321150.7101700599</v>
-      </c>
-      <c r="H8" s="31">
-        <v>2744570.1181608802</v>
-      </c>
-      <c r="I8" s="32">
-        <f>SUM(D8:H8)</f>
-        <v>5762098.6404351918</v>
-      </c>
-      <c r="J8" s="1"/>
-      <c r="K8" s="49"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
+      <c r="D17" s="19">
+        <v>0</v>
+      </c>
+      <c r="E17" s="19">
+        <v>0</v>
+      </c>
+      <c r="F17" s="19">
+        <v>0</v>
+      </c>
+      <c r="G17" s="20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
     </row>
-    <row r="9" spans="2:19" s="33" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B9" s="28" t="s">
+    <row r="18" spans="2:17" s="21" customFormat="1" ht="15" customHeight="1" outlineLevel="2">
+      <c r="B18" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="19">
+        <v>0</v>
+      </c>
+      <c r="D18" s="19">
+        <v>0</v>
+      </c>
+      <c r="E18" s="19">
+        <v>0</v>
+      </c>
+      <c r="F18" s="19">
+        <v>0</v>
+      </c>
+      <c r="G18" s="20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+    </row>
+    <row r="19" spans="2:17" s="21" customFormat="1" ht="15" customHeight="1" outlineLevel="2">
+      <c r="B19" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C19" s="19">
         <v>0</v>
       </c>
-      <c r="D9" s="30">
-        <v>3442</v>
-      </c>
-      <c r="E9" s="31">
-        <v>955462.17630225001</v>
-      </c>
-      <c r="F9" s="31">
-        <v>1090250.08894486</v>
-      </c>
-      <c r="G9" s="31">
-        <v>2080627.0666813899</v>
-      </c>
-      <c r="H9" s="31">
-        <v>1296753.8522276301</v>
-      </c>
-      <c r="I9" s="32">
-        <f>SUM(D9:H9)</f>
-        <v>5426535.1841561301</v>
-      </c>
-      <c r="J9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
+      <c r="D19" s="19">
+        <v>0</v>
+      </c>
+      <c r="E19" s="19">
+        <v>0</v>
+      </c>
+      <c r="F19" s="19">
+        <v>0</v>
+      </c>
+      <c r="G19" s="20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
     </row>
-    <row r="10" spans="2:19" s="33" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B10" s="28" t="s">
+    <row r="20" spans="2:17" s="21" customFormat="1" ht="15" customHeight="1" outlineLevel="2">
+      <c r="B20" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="29">
-        <v>6662282</v>
-      </c>
-      <c r="D10" s="30">
-        <v>1094764</v>
-      </c>
-      <c r="E10" s="31">
-        <v>871576.75637146505</v>
-      </c>
-      <c r="F10" s="31">
-        <v>990068.89531308005</v>
-      </c>
-      <c r="G10" s="31">
-        <v>1737122.4204106899</v>
-      </c>
-      <c r="H10" s="31">
-        <v>1564212.05660536</v>
-      </c>
-      <c r="I10" s="32">
-        <f>SUM(D10:H10)</f>
-        <v>6257744.1287005953</v>
-      </c>
-      <c r="J10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
+      <c r="C20" s="19">
+        <v>0</v>
+      </c>
+      <c r="D20" s="19">
+        <v>0</v>
+      </c>
+      <c r="E20" s="19">
+        <v>0</v>
+      </c>
+      <c r="F20" s="19">
+        <v>0</v>
+      </c>
+      <c r="G20" s="20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H20" s="1"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="33"/>
+      <c r="M20" s="33"/>
+      <c r="N20" s="33"/>
     </row>
-    <row r="11" spans="2:19" s="33" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B11" s="28" t="s">
+    <row r="21" spans="2:17" s="21" customFormat="1" ht="15" customHeight="1" outlineLevel="2">
+      <c r="B21" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="29">
-        <v>18430339</v>
-      </c>
-      <c r="D11" s="30">
-        <v>999027</v>
-      </c>
-      <c r="E11" s="31">
-        <v>410740.85847973399</v>
-      </c>
-      <c r="F11" s="31">
-        <v>519223.106757553</v>
-      </c>
-      <c r="G11" s="31">
-        <v>329478.02922197402</v>
-      </c>
-      <c r="H11" s="31">
-        <v>228707.318852753</v>
-      </c>
-      <c r="I11" s="32">
-        <f>SUM(D11:H11)</f>
-        <v>2487176.3133120141</v>
-      </c>
-      <c r="J11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
+      <c r="C21" s="19">
+        <v>0</v>
+      </c>
+      <c r="D21" s="19">
+        <v>0</v>
+      </c>
+      <c r="E21" s="19">
+        <v>0</v>
+      </c>
+      <c r="F21" s="19">
+        <v>0</v>
+      </c>
+      <c r="G21" s="20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="1"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="33"/>
+      <c r="M21" s="33"/>
+      <c r="N21" s="33"/>
     </row>
-    <row r="12" spans="2:19" s="33" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B12" s="28" t="s">
+    <row r="22" spans="2:17" ht="15" customHeight="1">
+      <c r="B22" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="31">
+        <f t="shared" ref="C22:G22" si="3">C23+C31+C38+C39</f>
+        <v>1492230.0177420087</v>
+      </c>
+      <c r="D22" s="31">
+        <f t="shared" si="3"/>
+        <v>1602496.7567783892</v>
+      </c>
+      <c r="E22" s="31">
+        <f t="shared" si="3"/>
+        <v>2812602.1255198307</v>
+      </c>
+      <c r="F22" s="31">
+        <f t="shared" si="3"/>
+        <v>2795714.1860899995</v>
+      </c>
+      <c r="G22" s="32">
+        <f t="shared" si="3"/>
+        <v>8703043.0861302279</v>
+      </c>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
+      <c r="N22" s="33"/>
+    </row>
+    <row r="23" spans="2:17" ht="15" customHeight="1">
+      <c r="B23" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="14">
+        <f>SUM(C24:C30)</f>
+        <v>1248484.5640498591</v>
+      </c>
+      <c r="D23" s="14">
+        <f>SUM(D24:D30)</f>
+        <v>1448152.299878753</v>
+      </c>
+      <c r="E23" s="14">
+        <f>SUM(E24:E30)</f>
+        <v>2744867.522950978</v>
+      </c>
+      <c r="F23" s="14">
+        <f>SUM(F24:F30)</f>
+        <v>2688149.7368793613</v>
+      </c>
+      <c r="G23" s="16">
+        <f t="shared" ref="G23:G39" si="4">SUM(C23:F23)</f>
+        <v>8129654.1237589512</v>
+      </c>
+      <c r="I23" s="58"/>
+      <c r="J23" s="58"/>
+      <c r="K23" s="58"/>
+      <c r="L23" s="58"/>
+      <c r="M23" s="28"/>
+      <c r="N23" s="33"/>
+      <c r="O23" s="33"/>
+      <c r="P23" s="33"/>
+      <c r="Q23" s="33"/>
+    </row>
+    <row r="24" spans="2:17" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B24" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="19">
+        <v>243496.43294691</v>
+      </c>
+      <c r="D24" s="19">
+        <v>403833.09416459303</v>
+      </c>
+      <c r="E24" s="19">
+        <v>1264324.5235389301</v>
+      </c>
+      <c r="F24" s="19">
+        <v>1429090.24878732</v>
+      </c>
+      <c r="G24" s="20">
+        <f t="shared" si="4"/>
+        <v>3340744.2994377529</v>
+      </c>
+      <c r="I24" s="58"/>
+      <c r="J24" s="58"/>
+      <c r="K24" s="58"/>
+      <c r="L24" s="58"/>
+      <c r="M24" s="33"/>
+      <c r="N24" s="33"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="33"/>
+      <c r="Q24" s="33"/>
+    </row>
+    <row r="25" spans="2:17" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B25" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="19">
+        <v>499658.99279393401</v>
+      </c>
+      <c r="D25" s="19">
+        <v>511272.83363597799</v>
+      </c>
+      <c r="E25" s="19">
+        <v>709389.90224992298</v>
+      </c>
+      <c r="F25" s="19">
+        <v>446018.55220764701</v>
+      </c>
+      <c r="G25" s="20">
+        <f t="shared" si="4"/>
+        <v>2166340.2808874818</v>
+      </c>
+      <c r="I25" s="58"/>
+      <c r="J25" s="58"/>
+      <c r="K25" s="58"/>
+      <c r="L25" s="58"/>
+      <c r="M25" s="33"/>
+      <c r="N25" s="33"/>
+      <c r="O25" s="33"/>
+      <c r="P25" s="33"/>
+      <c r="Q25" s="33"/>
+    </row>
+    <row r="26" spans="2:17" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B26" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="19">
+        <v>310174.01404482499</v>
+      </c>
+      <c r="D26" s="19">
+        <v>323630.628425673</v>
+      </c>
+      <c r="E26" s="19">
+        <v>508762.98930022301</v>
+      </c>
+      <c r="F26" s="19">
+        <v>508176.32777491701</v>
+      </c>
+      <c r="G26" s="20">
+        <f t="shared" si="4"/>
+        <v>1650743.9595456379</v>
+      </c>
+      <c r="I26" s="58"/>
+      <c r="J26" s="58"/>
+      <c r="K26" s="58"/>
+      <c r="L26" s="58"/>
+      <c r="M26" s="33"/>
+      <c r="N26" s="33"/>
+      <c r="O26" s="33"/>
+      <c r="P26" s="33"/>
+      <c r="Q26" s="33"/>
+    </row>
+    <row r="27" spans="2:17" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B27" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="19">
+        <v>131696.1005883</v>
+      </c>
+      <c r="D27" s="19">
+        <v>145709.90802411499</v>
+      </c>
+      <c r="E27" s="19">
+        <v>75987.725745175703</v>
+      </c>
+      <c r="F27" s="19">
+        <v>48172.766860030497</v>
+      </c>
+      <c r="G27" s="20">
+        <f t="shared" si="4"/>
+        <v>401566.50121762115</v>
+      </c>
+      <c r="I27" s="58"/>
+      <c r="J27" s="58"/>
+      <c r="K27" s="58"/>
+      <c r="L27" s="58"/>
+      <c r="M27" s="33"/>
+      <c r="N27" s="33"/>
+      <c r="O27" s="33"/>
+      <c r="P27" s="33"/>
+      <c r="Q27" s="33"/>
+    </row>
+    <row r="28" spans="2:17" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B28" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="19">
+        <v>15364.855731617699</v>
+      </c>
+      <c r="D28" s="19">
+        <v>15614.4001244835</v>
+      </c>
+      <c r="E28" s="19">
+        <v>23309.642380571298</v>
+      </c>
+      <c r="F28" s="19">
+        <v>24551.7199398628</v>
+      </c>
+      <c r="G28" s="20">
+        <f t="shared" si="4"/>
+        <v>78840.618176535296</v>
+      </c>
+      <c r="I28" s="58"/>
+      <c r="J28" s="58"/>
+      <c r="K28" s="58"/>
+      <c r="L28" s="58"/>
+      <c r="M28" s="33"/>
+      <c r="N28" s="33"/>
+      <c r="O28" s="33"/>
+      <c r="P28" s="33"/>
+      <c r="Q28" s="33"/>
+    </row>
+    <row r="29" spans="2:17" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B29" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="19">
+        <v>48094.167944272398</v>
+      </c>
+      <c r="D29" s="19">
+        <v>48091.435503910201</v>
+      </c>
+      <c r="E29" s="19">
+        <v>163092.739736155</v>
+      </c>
+      <c r="F29" s="19">
+        <v>232140.12130958401</v>
+      </c>
+      <c r="G29" s="20">
+        <f t="shared" si="4"/>
+        <v>491418.46449392161</v>
+      </c>
+      <c r="I29" s="58"/>
+      <c r="J29" s="58"/>
+      <c r="K29" s="58"/>
+      <c r="L29" s="58"/>
+      <c r="M29" s="33"/>
+      <c r="N29" s="33"/>
+      <c r="O29" s="33"/>
+      <c r="P29" s="33"/>
+      <c r="Q29" s="33"/>
+    </row>
+    <row r="30" spans="2:17" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B30" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="29">
-        <v>12153534</v>
-      </c>
-      <c r="D12" s="30">
-        <v>333510</v>
-      </c>
-      <c r="E12" s="31">
-        <v>55694.6124072233</v>
-      </c>
-      <c r="F12" s="31">
-        <v>63247.722184106402</v>
-      </c>
-      <c r="G12" s="31">
-        <v>109498.235406874</v>
-      </c>
-      <c r="H12" s="31">
-        <v>100261.487526592</v>
-      </c>
-      <c r="I12" s="32">
-        <f>SUM(D12:H12)</f>
-        <v>662212.05752479576</v>
-      </c>
-      <c r="J12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="20">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="59"/>
+      <c r="L30" s="59"/>
+      <c r="M30" s="60"/>
+      <c r="N30" s="33"/>
+      <c r="O30" s="33"/>
+      <c r="P30" s="33"/>
+      <c r="Q30" s="33"/>
     </row>
-    <row r="13" spans="2:19" s="33" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B13" s="28" t="s">
+    <row r="31" spans="2:17" ht="15" customHeight="1">
+      <c r="B31" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="29">
-        <v>2284955</v>
-      </c>
-      <c r="D13" s="30">
-        <v>84495</v>
-      </c>
-      <c r="E13" s="31">
-        <v>53350.320363603103</v>
-      </c>
-      <c r="F13" s="31">
-        <v>56479.916130589401</v>
-      </c>
-      <c r="G13" s="31">
-        <v>271153.056672687</v>
-      </c>
-      <c r="H13" s="31">
-        <v>399223.89661282598</v>
-      </c>
-      <c r="I13" s="32">
-        <f>SUM(D13:H13)</f>
-        <v>864702.18977970548</v>
-      </c>
-      <c r="J13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
+      <c r="C31" s="24">
+        <v>200000</v>
+      </c>
+      <c r="D31" s="24">
+        <v>150000</v>
+      </c>
+      <c r="E31" s="24">
+        <v>59500</v>
+      </c>
+      <c r="F31" s="24">
+        <v>59500</v>
+      </c>
+      <c r="G31" s="27">
+        <f t="shared" si="4"/>
+        <v>469000</v>
+      </c>
+      <c r="K31" s="59"/>
+      <c r="L31" s="61"/>
+      <c r="M31" s="61"/>
     </row>
-    <row r="14" spans="2:19" s="33" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B14" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="29">
-        <v>7100</v>
-      </c>
-      <c r="D14" s="30">
-        <v>200</v>
-      </c>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="32">
-        <f>SUM(D14:H14)</f>
-        <v>200</v>
-      </c>
-      <c r="J14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
+    <row r="32" spans="2:17" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B32" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="19">
+        <v>200000</v>
+      </c>
+      <c r="D32" s="19">
+        <v>150000</v>
+      </c>
+      <c r="E32" s="19">
+        <v>59500</v>
+      </c>
+      <c r="F32" s="19">
+        <v>59500</v>
+      </c>
+      <c r="G32" s="20">
+        <f t="shared" si="4"/>
+        <v>469000</v>
+      </c>
     </row>
-    <row r="15" spans="2:19" ht="15" customHeight="1">
-      <c r="B15" s="35" t="s">
+    <row r="33" spans="2:10" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B33" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="19">
+        <v>0</v>
+      </c>
+      <c r="D33" s="19">
+        <v>0</v>
+      </c>
+      <c r="E33" s="19">
+        <v>0</v>
+      </c>
+      <c r="F33" s="19">
+        <v>0</v>
+      </c>
+      <c r="G33" s="20">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B34" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="19">
+        <v>0</v>
+      </c>
+      <c r="D34" s="19">
+        <v>0</v>
+      </c>
+      <c r="E34" s="19">
+        <v>0</v>
+      </c>
+      <c r="F34" s="19">
+        <v>0</v>
+      </c>
+      <c r="G34" s="20">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B35" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="19">
+        <v>0</v>
+      </c>
+      <c r="D35" s="19">
+        <v>0</v>
+      </c>
+      <c r="E35" s="19">
+        <v>0</v>
+      </c>
+      <c r="F35" s="19">
+        <v>0</v>
+      </c>
+      <c r="G35" s="20">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B36" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="19">
+        <v>0</v>
+      </c>
+      <c r="D36" s="19">
+        <v>0</v>
+      </c>
+      <c r="E36" s="19">
+        <v>0</v>
+      </c>
+      <c r="F36" s="19">
+        <v>0</v>
+      </c>
+      <c r="G36" s="20">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" ht="15" customHeight="1" outlineLevel="1">
+      <c r="B37" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="20">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" ht="15" customHeight="1">
+      <c r="B38" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="36">
-        <v>4197583</v>
-      </c>
-      <c r="D15" s="37">
-        <v>20527</v>
-      </c>
-      <c r="E15" s="39">
-        <v>541569</v>
-      </c>
-      <c r="F15" s="39">
-        <v>406146</v>
-      </c>
-      <c r="G15" s="39">
-        <v>161130</v>
-      </c>
-      <c r="H15" s="40">
-        <v>161130</v>
-      </c>
-      <c r="I15" s="41">
-        <f>SUM(D15:H15)</f>
-        <v>1290502</v>
-      </c>
-      <c r="K15" s="42"/>
-      <c r="O15" s="42"/>
-      <c r="P15" s="42"/>
-      <c r="Q15" s="42"/>
-      <c r="R15" s="42"/>
-      <c r="S15" s="42"/>
+      <c r="C38" s="35">
+        <v>40000</v>
+      </c>
+      <c r="D38" s="35">
+        <v>0</v>
+      </c>
+      <c r="E38" s="35">
+        <v>0</v>
+      </c>
+      <c r="F38" s="35">
+        <v>40000</v>
+      </c>
+      <c r="G38" s="36">
+        <f t="shared" si="4"/>
+        <v>80000</v>
+      </c>
     </row>
-    <row r="16" spans="2:19" s="33" customFormat="1" ht="15" customHeight="1" outlineLevel="2">
-      <c r="B16" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="29">
+    <row r="39" spans="2:10" ht="15" customHeight="1">
+      <c r="B39" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" s="38">
+        <v>3745.453692149571</v>
+      </c>
+      <c r="D39" s="38">
+        <v>4344.4568996362541</v>
+      </c>
+      <c r="E39" s="38">
+        <v>8234.6025688529298</v>
+      </c>
+      <c r="F39" s="38">
+        <v>8064.4492106381022</v>
+      </c>
+      <c r="G39" s="39">
+        <f t="shared" si="4"/>
+        <v>24388.962371276859</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" ht="15" customHeight="1">
+      <c r="B40" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" s="42">
+        <f t="shared" ref="C40:G40" si="5">IFERROR(((C7+C15)-(C23+C31))/(C7+C15),0)</f>
+        <v>0.54029026762224486</v>
+      </c>
+      <c r="D40" s="42">
+        <f t="shared" si="5"/>
+        <v>0.55099499017624232</v>
+      </c>
+      <c r="E40" s="42">
+        <f t="shared" si="5"/>
+        <v>0.59995667494802307</v>
+      </c>
+      <c r="F40" s="42">
+        <f t="shared" si="5"/>
+        <v>0.57695003831357139</v>
+      </c>
+      <c r="G40" s="41">
+        <f t="shared" si="5"/>
+        <v>0.57464423906831319</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" ht="15" customHeight="1">
+      <c r="B41" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C41" s="31">
+        <f t="shared" ref="C41:G41" si="6">SUM(C42:C44)</f>
+        <v>623134.37634510128</v>
+      </c>
+      <c r="D41" s="31">
+        <f t="shared" si="6"/>
+        <v>701382.85822907614</v>
+      </c>
+      <c r="E41" s="31">
+        <f t="shared" si="6"/>
+        <v>1333493.5720040328</v>
+      </c>
+      <c r="F41" s="31">
+        <f t="shared" si="6"/>
+        <v>1213704.2374957125</v>
+      </c>
+      <c r="G41" s="32">
+        <f t="shared" si="6"/>
+        <v>3871715.0440739226</v>
+      </c>
+      <c r="I41" s="33"/>
+    </row>
+    <row r="42" spans="2:10" ht="15" customHeight="1">
+      <c r="B42" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" s="44">
+        <v>520951.546156422</v>
+      </c>
+      <c r="D42" s="44">
+        <v>624751.53747435915</v>
+      </c>
+      <c r="E42" s="44">
+        <v>1303091.68521158</v>
+      </c>
+      <c r="F42" s="44">
+        <v>1183302.3507032597</v>
+      </c>
+      <c r="G42" s="45">
+        <f>SUM(C42:F42)</f>
+        <v>3632097.1195456209</v>
+      </c>
+      <c r="I42" s="33"/>
+    </row>
+    <row r="43" spans="2:10" ht="15" customHeight="1">
+      <c r="B43" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="35">
+        <v>102182.83018867925</v>
+      </c>
+      <c r="D43" s="35">
+        <v>76631.320754716988</v>
+      </c>
+      <c r="E43" s="35">
+        <v>30401.886792452831</v>
+      </c>
+      <c r="F43" s="35">
+        <v>30401.886792452831</v>
+      </c>
+      <c r="G43" s="36">
+        <f>SUM(C43:F43)</f>
+        <v>239617.9245283019</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" ht="15" customHeight="1">
+      <c r="B44" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" s="38">
         <v>0</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D44" s="38">
         <v>0</v>
       </c>
-      <c r="E16" s="31">
-        <f>E15</f>
-        <v>541569</v>
-      </c>
-      <c r="F16" s="31">
-        <f>F15</f>
-        <v>406146</v>
-      </c>
-      <c r="G16" s="31">
-        <f>G15</f>
-        <v>161130</v>
-      </c>
-      <c r="H16" s="31">
-        <f>H15</f>
-        <v>161130</v>
-      </c>
-      <c r="I16" s="32">
-        <f>SUM(D16:H16)</f>
-        <v>1269975</v>
-      </c>
-      <c r="J16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
+      <c r="E44" s="38">
+        <v>0</v>
+      </c>
+      <c r="F44" s="38">
+        <v>0</v>
+      </c>
+      <c r="G44" s="39">
+        <f>SUM(C44:F44)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="2:19" s="33" customFormat="1" ht="15" customHeight="1" outlineLevel="2">
-      <c r="B17" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="29">
+    <row r="45" spans="2:10" ht="15" customHeight="1">
+      <c r="B45" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" s="46">
+        <f t="shared" ref="C45:G45" si="7">IFERROR((C15+C7)/(C42+C43),0)</f>
+        <v>5.056481966695463</v>
+      </c>
+      <c r="D45" s="46">
+        <f t="shared" si="7"/>
+        <v>5.0747170204995102</v>
+      </c>
+      <c r="E45" s="46">
+        <f t="shared" si="7"/>
+        <v>5.2569878593629058</v>
+      </c>
+      <c r="F45" s="46">
+        <f t="shared" si="7"/>
+        <v>5.3512697157481792</v>
+      </c>
+      <c r="G45" s="47">
+        <f t="shared" si="7"/>
+        <v>5.2212534455111781</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" ht="15" customHeight="1">
+      <c r="B46" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" s="49">
+        <f t="shared" ref="C46:F46" si="8">C22-C41</f>
+        <v>869095.64139690739</v>
+      </c>
+      <c r="D46" s="49">
+        <f t="shared" si="8"/>
+        <v>901113.89854931307</v>
+      </c>
+      <c r="E46" s="49">
+        <f t="shared" si="8"/>
+        <v>1479108.5535157979</v>
+      </c>
+      <c r="F46" s="49">
+        <f t="shared" si="8"/>
+        <v>1582009.948594287</v>
+      </c>
+      <c r="G46" s="50">
+        <f>SUM(C46:F46)</f>
+        <v>4831328.0420563053</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" ht="15" customHeight="1">
+      <c r="B47" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47" s="53">
+        <f t="shared" ref="C47:G47" si="9">IFERROR(C46/C$22,0)</f>
+        <v>0.58241399185361054</v>
+      </c>
+      <c r="D47" s="53">
+        <f t="shared" si="9"/>
+        <v>0.56231870344679202</v>
+      </c>
+      <c r="E47" s="53">
+        <f t="shared" si="9"/>
+        <v>0.52588616786401177</v>
+      </c>
+      <c r="F47" s="53">
+        <f t="shared" si="9"/>
+        <v>0.56586970029537886</v>
+      </c>
+      <c r="G47" s="52">
+        <f t="shared" si="9"/>
+        <v>0.55513088861479321</v>
+      </c>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+    </row>
+    <row r="48" spans="2:10" ht="15" customHeight="1">
+      <c r="B48" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" s="31">
+        <f t="shared" ref="C48:G48" si="10">SUM(C49:C53)</f>
+        <v>663631.97002070153</v>
+      </c>
+      <c r="D48" s="31">
+        <f t="shared" si="10"/>
+        <v>769765.35500055028</v>
+      </c>
+      <c r="E48" s="31">
+        <f t="shared" si="10"/>
+        <v>1459034.3318245916</v>
+      </c>
+      <c r="F48" s="31">
+        <f t="shared" si="10"/>
+        <v>1428885.9926382275</v>
+      </c>
+      <c r="G48" s="32">
+        <f t="shared" si="10"/>
+        <v>4321317.6494840709</v>
+      </c>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+    </row>
+    <row r="49" spans="2:10" ht="15" customHeight="1">
+      <c r="B49" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C49" s="44">
+        <v>282844.17798549513</v>
+      </c>
+      <c r="D49" s="44">
+        <v>328078.90353753115</v>
+      </c>
+      <c r="E49" s="44">
+        <v>621849.73732454376</v>
+      </c>
+      <c r="F49" s="44">
+        <v>609000.32289002067</v>
+      </c>
+      <c r="G49" s="45">
+        <f>SUM(C49:F49)</f>
+        <v>1841773.1417375908</v>
+      </c>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+    </row>
+    <row r="50" spans="2:10" ht="15" customHeight="1">
+      <c r="B50" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="35">
+        <v>112363.61076448712</v>
+      </c>
+      <c r="D50" s="35">
+        <v>130333.70698908762</v>
+      </c>
+      <c r="E50" s="35">
+        <v>247038.07706558789</v>
+      </c>
+      <c r="F50" s="35">
+        <v>241933.47631914305</v>
+      </c>
+      <c r="G50" s="36">
+        <f>SUM(C50:F50)</f>
+        <v>731668.87113830575</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" ht="15" customHeight="1">
+      <c r="B51" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51" s="35">
+        <v>118606.03358473642</v>
+      </c>
+      <c r="D51" s="35">
+        <v>137574.46848848139</v>
+      </c>
+      <c r="E51" s="35">
+        <v>260762.41468034277</v>
+      </c>
+      <c r="F51" s="35">
+        <v>255374.2250035399</v>
+      </c>
+      <c r="G51" s="36">
+        <f>SUM(C51:F51)</f>
+        <v>772317.14175710047</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" ht="15" customHeight="1">
+      <c r="B52" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C52" s="35">
+        <v>149818.14768598284</v>
+      </c>
+      <c r="D52" s="35">
+        <v>173778.27598545016</v>
+      </c>
+      <c r="E52" s="35">
+        <v>329384.10275411716</v>
+      </c>
+      <c r="F52" s="35">
+        <v>322577.96842552407</v>
+      </c>
+      <c r="G52" s="36">
+        <f>SUM(C52:F52)</f>
+        <v>975558.4948510743</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" ht="15" customHeight="1">
+      <c r="B53" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" s="35">
         <v>0</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D53" s="35">
         <v>0</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E53" s="35">
         <v>0</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F53" s="35">
         <v>0</v>
       </c>
-      <c r="G17" s="31">
+      <c r="G53" s="36">
+        <f>SUM(C53:F53)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="31">
-        <v>0</v>
-      </c>
-      <c r="I17" s="32">
-        <f>SUM(D17:H17)</f>
-        <v>0</v>
-      </c>
-      <c r="J17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
     </row>
-    <row r="18" spans="2:19" s="33" customFormat="1" ht="15" customHeight="1" outlineLevel="2">
-      <c r="B18" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="29">
-        <v>1463376</v>
-      </c>
-      <c r="D18" s="30">
-        <v>20110</v>
-      </c>
-      <c r="E18" s="31">
-        <v>0</v>
-      </c>
-      <c r="F18" s="31">
-        <v>0</v>
-      </c>
-      <c r="G18" s="31">
-        <v>0</v>
-      </c>
-      <c r="H18" s="31">
-        <v>0</v>
-      </c>
-      <c r="I18" s="32">
-        <f>SUM(D18:H18)</f>
-        <v>20110</v>
-      </c>
-      <c r="J18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
+    <row r="54" spans="2:10" ht="15" customHeight="1">
+      <c r="B54" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="C54" s="49">
+        <f t="shared" ref="C54:G54" si="11">C46-C48</f>
+        <v>205463.67137620586</v>
+      </c>
+      <c r="D54" s="49">
+        <f t="shared" si="11"/>
+        <v>131348.5435487628</v>
+      </c>
+      <c r="E54" s="49">
+        <f t="shared" si="11"/>
+        <v>20074.22169120633</v>
+      </c>
+      <c r="F54" s="49">
+        <f t="shared" si="11"/>
+        <v>153123.95595605951</v>
+      </c>
+      <c r="G54" s="50">
+        <f t="shared" si="11"/>
+        <v>510010.39257223438</v>
+      </c>
     </row>
-    <row r="19" spans="2:19" s="33" customFormat="1" ht="15" customHeight="1" outlineLevel="2">
-      <c r="B19" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="29">
-        <v>2581013</v>
-      </c>
-      <c r="D19" s="30">
-        <v>252</v>
-      </c>
-      <c r="E19" s="31">
-        <v>0</v>
-      </c>
-      <c r="F19" s="31">
-        <v>0</v>
-      </c>
-      <c r="G19" s="31">
-        <v>0</v>
-      </c>
-      <c r="H19" s="31">
-        <v>0</v>
-      </c>
-      <c r="I19" s="32">
-        <f>SUM(D19:H19)</f>
-        <v>252</v>
-      </c>
-      <c r="J19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
+    <row r="55" spans="2:10" ht="15" customHeight="1">
+      <c r="B55" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55" s="53">
+        <f t="shared" ref="C55:G55" si="12">IFERROR(C54/C$22,0)</f>
+        <v>0.13768900835214831</v>
+      </c>
+      <c r="D55" s="53">
+        <f t="shared" si="12"/>
+        <v>8.1964935650055179E-2</v>
+      </c>
+      <c r="E55" s="53">
+        <f t="shared" si="12"/>
+        <v>7.1372418832600336E-3</v>
+      </c>
+      <c r="F55" s="53">
+        <f t="shared" si="12"/>
+        <v>5.4770962181300085E-2</v>
+      </c>
+      <c r="G55" s="52">
+        <f t="shared" si="12"/>
+        <v>5.8601386609819534E-2</v>
+      </c>
     </row>
-    <row r="20" spans="2:19" s="33" customFormat="1" ht="15" customHeight="1" outlineLevel="2">
-      <c r="B20" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="29">
-        <v>-26902</v>
-      </c>
-      <c r="D20" s="30">
-        <v>0</v>
-      </c>
-      <c r="E20" s="31">
-        <v>0</v>
-      </c>
-      <c r="F20" s="31">
-        <v>0</v>
-      </c>
-      <c r="G20" s="31">
-        <v>0</v>
-      </c>
-      <c r="H20" s="31">
-        <v>0</v>
-      </c>
-      <c r="I20" s="32">
-        <f>SUM(D20:H20)</f>
-        <v>0</v>
-      </c>
-      <c r="J20" s="1"/>
-      <c r="K20" s="49"/>
-      <c r="L20" s="49"/>
-      <c r="M20" s="49"/>
-      <c r="N20" s="49"/>
-      <c r="O20" s="49"/>
-      <c r="P20" s="49"/>
+    <row r="56" spans="2:10" ht="15" customHeight="1">
+      <c r="B56" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="C56" s="31">
+        <f t="shared" ref="C56:G56" si="13">SUM(C57:C64)</f>
+        <v>560530.41662807029</v>
+      </c>
+      <c r="D56" s="31">
+        <f t="shared" si="13"/>
+        <v>604950.61773333338</v>
+      </c>
+      <c r="E56" s="31">
+        <f t="shared" si="13"/>
+        <v>648505.95773333334</v>
+      </c>
+      <c r="F56" s="31">
+        <f t="shared" si="13"/>
+        <v>633665.61773333338</v>
+      </c>
+      <c r="G56" s="32">
+        <f t="shared" si="13"/>
+        <v>2447652.6098280703</v>
+      </c>
     </row>
-    <row r="21" spans="2:19" s="33" customFormat="1" ht="15" customHeight="1" outlineLevel="2">
-      <c r="B21" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="29">
-        <v>180096</v>
-      </c>
-      <c r="D21" s="30">
-        <v>165</v>
-      </c>
-      <c r="E21" s="31">
-        <v>0</v>
-      </c>
-      <c r="F21" s="31">
-        <v>0</v>
-      </c>
-      <c r="G21" s="31">
-        <v>0</v>
-      </c>
-      <c r="H21" s="31">
-        <v>0</v>
-      </c>
-      <c r="I21" s="32">
-        <f>SUM(D21:H21)</f>
-        <v>165</v>
-      </c>
-      <c r="J21" s="1"/>
-      <c r="K21" s="49"/>
-      <c r="L21" s="49"/>
-      <c r="M21" s="49"/>
-      <c r="N21" s="49"/>
-      <c r="O21" s="49"/>
-      <c r="P21" s="49"/>
+    <row r="57" spans="2:10" ht="15" customHeight="1">
+      <c r="B57" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="C57" s="44">
+        <v>347835.1266280702</v>
+      </c>
+      <c r="D57" s="44">
+        <v>353895.66773333331</v>
+      </c>
+      <c r="E57" s="44">
+        <v>383310.66773333331</v>
+      </c>
+      <c r="F57" s="44">
+        <v>368110.66773333331</v>
+      </c>
+      <c r="G57" s="45">
+        <f t="shared" ref="G57:G64" si="14">SUM(C57:F57)</f>
+        <v>1453152.1298280701</v>
+      </c>
+      <c r="H57" s="17"/>
+      <c r="I57" s="17"/>
     </row>
-    <row r="22" spans="2:19" ht="15" customHeight="1">
-      <c r="B22" s="44" t="s">
+    <row r="58" spans="2:10" ht="15" customHeight="1">
+      <c r="B58" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C58" s="35">
+        <v>50000</v>
+      </c>
+      <c r="D58" s="35">
+        <v>50000</v>
+      </c>
+      <c r="E58" s="35">
+        <v>50000</v>
+      </c>
+      <c r="F58" s="35">
+        <v>50000</v>
+      </c>
+      <c r="G58" s="36">
+        <f t="shared" si="14"/>
+        <v>200000</v>
+      </c>
+      <c r="H58" s="17"/>
+      <c r="I58" s="17"/>
+    </row>
+    <row r="59" spans="2:10" ht="15" customHeight="1">
+      <c r="B59" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="35">
+        <v>3500</v>
+      </c>
+      <c r="D59" s="35">
+        <v>3500</v>
+      </c>
+      <c r="E59" s="35">
+        <v>3500</v>
+      </c>
+      <c r="F59" s="35">
+        <v>3500</v>
+      </c>
+      <c r="G59" s="36">
+        <f t="shared" si="14"/>
+        <v>14000</v>
+      </c>
+      <c r="H59" s="17"/>
+      <c r="I59" s="17"/>
+    </row>
+    <row r="60" spans="2:10" ht="15" customHeight="1">
+      <c r="B60" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C60" s="35">
+        <v>23987.63</v>
+      </c>
+      <c r="D60" s="35">
+        <v>26847.289999999997</v>
+      </c>
+      <c r="E60" s="35">
+        <v>23987.63</v>
+      </c>
+      <c r="F60" s="35">
+        <v>26847.289999999997</v>
+      </c>
+      <c r="G60" s="36">
+        <f t="shared" si="14"/>
+        <v>101669.84</v>
+      </c>
+      <c r="H60" s="17"/>
+      <c r="I60" s="17"/>
+    </row>
+    <row r="61" spans="2:10" ht="15" customHeight="1">
+      <c r="B61" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="C61" s="35">
+        <v>2000</v>
+      </c>
+      <c r="D61" s="35">
+        <v>37500</v>
+      </c>
+      <c r="E61" s="35">
+        <v>4500</v>
+      </c>
+      <c r="F61" s="35">
+        <v>2000</v>
+      </c>
+      <c r="G61" s="36">
+        <f t="shared" si="14"/>
+        <v>46000</v>
+      </c>
+      <c r="H61" s="17"/>
+      <c r="I61" s="17"/>
+    </row>
+    <row r="62" spans="2:10" ht="15" customHeight="1">
+      <c r="B62" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C62" s="35">
+        <v>100000</v>
+      </c>
+      <c r="D62" s="35">
+        <v>100000</v>
+      </c>
+      <c r="E62" s="35">
+        <v>150000</v>
+      </c>
+      <c r="F62" s="35">
+        <v>150000</v>
+      </c>
+      <c r="G62" s="36">
+        <f t="shared" si="14"/>
+        <v>500000</v>
+      </c>
+      <c r="H62" s="17"/>
+      <c r="I62" s="17"/>
+    </row>
+    <row r="63" spans="2:10" ht="15" customHeight="1">
+      <c r="B63" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C63" s="35">
+        <v>8207.66</v>
+      </c>
+      <c r="D63" s="35">
+        <v>8207.66</v>
+      </c>
+      <c r="E63" s="35">
+        <v>8207.66</v>
+      </c>
+      <c r="F63" s="35">
+        <v>8207.66</v>
+      </c>
+      <c r="G63" s="36">
+        <f t="shared" si="14"/>
+        <v>32830.639999999999</v>
+      </c>
+      <c r="H63" s="17"/>
+      <c r="I63" s="17"/>
+    </row>
+    <row r="64" spans="2:10" ht="15" customHeight="1">
+      <c r="B64" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="45">
-        <v>22818775.59</v>
-      </c>
-      <c r="D22" s="46">
-        <f t="shared" ref="D22:I22" si="2">D23+D31+D38+D39</f>
-        <v>1175480.0300000003</v>
-      </c>
-      <c r="E22" s="47">
-        <f t="shared" si="2"/>
-        <v>1492230.0177420087</v>
-      </c>
-      <c r="F22" s="47">
-        <f t="shared" si="2"/>
-        <v>1602496.7567783892</v>
-      </c>
-      <c r="G22" s="47">
-        <f t="shared" si="2"/>
-        <v>2812602.1255198307</v>
-      </c>
-      <c r="H22" s="47">
-        <f t="shared" si="2"/>
-        <v>2795714.1860899995</v>
-      </c>
-      <c r="I22" s="48">
-        <f t="shared" si="2"/>
-        <v>9878523.1161302272</v>
-      </c>
-      <c r="K22" s="49"/>
-      <c r="L22" s="49"/>
-      <c r="M22" s="49"/>
-      <c r="N22" s="49"/>
-      <c r="O22" s="49"/>
-      <c r="P22" s="49"/>
+      <c r="C64" s="35">
+        <v>25000</v>
+      </c>
+      <c r="D64" s="35">
+        <v>25000</v>
+      </c>
+      <c r="E64" s="35">
+        <v>25000</v>
+      </c>
+      <c r="F64" s="35">
+        <v>25000</v>
+      </c>
+      <c r="G64" s="36">
+        <f t="shared" si="14"/>
+        <v>100000</v>
+      </c>
+      <c r="H64" s="17"/>
+      <c r="I64" s="17"/>
     </row>
-    <row r="23" spans="2:19" ht="15" customHeight="1">
-      <c r="B23" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="22">
-        <v>20321706.57</v>
-      </c>
-      <c r="D23" s="23">
-        <v>1170297.4900000002</v>
-      </c>
-      <c r="E23" s="24">
-        <f>SUM(E24:E30)</f>
-        <v>1248484.5640498591</v>
-      </c>
-      <c r="F23" s="24">
-        <f>SUM(F24:F30)</f>
-        <v>1448152.299878753</v>
-      </c>
-      <c r="G23" s="24">
-        <f>SUM(G24:G30)</f>
-        <v>2744867.522950978</v>
-      </c>
-      <c r="H23" s="24">
-        <f>SUM(H24:H30)</f>
-        <v>2688149.7368793613</v>
-      </c>
-      <c r="I23" s="26">
-        <f>SUM(D23:H23)</f>
-        <v>9299951.6137589514</v>
-      </c>
-      <c r="K23" s="98"/>
-      <c r="L23" s="98"/>
-      <c r="M23" s="98"/>
-      <c r="N23" s="98"/>
-      <c r="O23" s="42"/>
-      <c r="P23" s="49"/>
-      <c r="Q23" s="49"/>
-      <c r="R23" s="49"/>
-      <c r="S23" s="49"/>
+    <row r="65" spans="2:11" ht="15" customHeight="1">
+      <c r="B65" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="C65" s="49">
+        <f t="shared" ref="C65:G65" si="15">C54-C56</f>
+        <v>-355066.74525186443</v>
+      </c>
+      <c r="D65" s="49">
+        <f t="shared" si="15"/>
+        <v>-473602.07418457058</v>
+      </c>
+      <c r="E65" s="49">
+        <f t="shared" si="15"/>
+        <v>-628431.73604212701</v>
+      </c>
+      <c r="F65" s="49">
+        <f t="shared" si="15"/>
+        <v>-480541.66177727387</v>
+      </c>
+      <c r="G65" s="50">
+        <f t="shared" si="15"/>
+        <v>-1937642.2172558359</v>
+      </c>
+      <c r="H65" s="17"/>
+      <c r="I65" s="17"/>
     </row>
-    <row r="24" spans="2:19" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B24" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="29"/>
-      <c r="D24" s="30">
-        <v>0</v>
-      </c>
-      <c r="E24" s="31">
-        <v>243496.43294691</v>
-      </c>
-      <c r="F24" s="31">
-        <v>403833.09416459303</v>
-      </c>
-      <c r="G24" s="31">
-        <v>1264324.5235389301</v>
-      </c>
-      <c r="H24" s="31">
-        <v>1429090.24878732</v>
-      </c>
-      <c r="I24" s="32">
-        <f>SUM(D24:H24)</f>
-        <v>3340744.2994377529</v>
-      </c>
-      <c r="K24" s="98"/>
-      <c r="L24" s="98"/>
-      <c r="M24" s="98"/>
-      <c r="N24" s="98"/>
-      <c r="O24" s="49"/>
-      <c r="P24" s="49"/>
-      <c r="Q24" s="49"/>
-      <c r="R24" s="49"/>
-      <c r="S24" s="49"/>
+    <row r="66" spans="2:11" ht="15" customHeight="1">
+      <c r="B66" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="C66" s="56">
+        <f t="shared" ref="C66:G66" si="16">IFERROR(C65/C$22,0)</f>
+        <v>-0.23794370909998128</v>
+      </c>
+      <c r="D66" s="56">
+        <f t="shared" si="16"/>
+        <v>-0.29554011400103286</v>
+      </c>
+      <c r="E66" s="56">
+        <f t="shared" si="16"/>
+        <v>-0.2234342818488694</v>
+      </c>
+      <c r="F66" s="56">
+        <f t="shared" si="16"/>
+        <v>-0.17188511764478498</v>
+      </c>
+      <c r="G66" s="55">
+        <f t="shared" si="16"/>
+        <v>-0.22263962134621587</v>
+      </c>
+      <c r="H66" s="17"/>
+      <c r="I66" s="17"/>
     </row>
-    <row r="25" spans="2:19" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B25" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="29"/>
-      <c r="D25" s="30">
-        <v>3371.52</v>
-      </c>
-      <c r="E25" s="31">
-        <v>499658.99279393401</v>
-      </c>
-      <c r="F25" s="31">
-        <v>511272.83363597799</v>
-      </c>
-      <c r="G25" s="31">
-        <v>709389.90224992298</v>
-      </c>
-      <c r="H25" s="31">
-        <v>446018.55220764701</v>
-      </c>
-      <c r="I25" s="32">
-        <f>SUM(D25:H25)</f>
-        <v>2169711.8008874818</v>
-      </c>
-      <c r="K25" s="98"/>
-      <c r="L25" s="98"/>
-      <c r="M25" s="98"/>
-      <c r="N25" s="98"/>
-      <c r="O25" s="49"/>
-      <c r="P25" s="49"/>
-      <c r="Q25" s="49"/>
-      <c r="R25" s="49"/>
-      <c r="S25" s="49"/>
+    <row r="67" spans="2:11">
+      <c r="H67" s="17"/>
+      <c r="I67" s="17"/>
     </row>
-    <row r="26" spans="2:19" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B26" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" s="29"/>
-      <c r="D26" s="30">
-        <v>642208.79</v>
-      </c>
-      <c r="E26" s="31">
-        <v>310174.01404482499</v>
-      </c>
-      <c r="F26" s="31">
-        <v>323630.628425673</v>
-      </c>
-      <c r="G26" s="31">
-        <v>508762.98930022301</v>
-      </c>
-      <c r="H26" s="31">
-        <v>508176.32777491701</v>
-      </c>
-      <c r="I26" s="32">
-        <f>SUM(D26:H26)</f>
-        <v>2292952.7495456384</v>
-      </c>
-      <c r="K26" s="98"/>
-      <c r="L26" s="98"/>
-      <c r="M26" s="98"/>
-      <c r="N26" s="98"/>
-      <c r="O26" s="49"/>
-      <c r="P26" s="49"/>
-      <c r="Q26" s="49"/>
-      <c r="R26" s="49"/>
-      <c r="S26" s="49"/>
+    <row r="68" spans="2:11">
+      <c r="C68" s="62"/>
+      <c r="D68" s="62"/>
+      <c r="E68" s="62"/>
+      <c r="F68" s="62"/>
+      <c r="G68" s="62"/>
+      <c r="H68" s="17"/>
+      <c r="I68" s="17"/>
     </row>
-    <row r="27" spans="2:19" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B27" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="29"/>
-      <c r="D27" s="30">
-        <v>352267.57999999996</v>
-      </c>
-      <c r="E27" s="31">
-        <v>131696.1005883</v>
-      </c>
-      <c r="F27" s="31">
-        <v>145709.90802411499</v>
-      </c>
-      <c r="G27" s="31">
-        <v>75987.725745175703</v>
-      </c>
-      <c r="H27" s="31">
-        <v>48172.766860030497</v>
-      </c>
-      <c r="I27" s="32">
-        <f>SUM(D27:H27)</f>
-        <v>753834.08121762122</v>
-      </c>
-      <c r="K27" s="98"/>
-      <c r="L27" s="98"/>
-      <c r="M27" s="98"/>
-      <c r="N27" s="98"/>
-      <c r="O27" s="49"/>
-      <c r="P27" s="49"/>
-      <c r="Q27" s="49"/>
-      <c r="R27" s="49"/>
-      <c r="S27" s="49"/>
+    <row r="69" spans="2:11">
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="H69" s="17"/>
+      <c r="I69" s="17"/>
+      <c r="K69" s="63"/>
     </row>
-    <row r="28" spans="2:19" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B28" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="29"/>
-      <c r="D28" s="30">
-        <v>108628.95000000027</v>
-      </c>
-      <c r="E28" s="31">
-        <v>15364.855731617699</v>
-      </c>
-      <c r="F28" s="31">
-        <v>15614.4001244835</v>
-      </c>
-      <c r="G28" s="31">
-        <v>23309.642380571298</v>
-      </c>
-      <c r="H28" s="31">
-        <v>24551.7199398628</v>
-      </c>
-      <c r="I28" s="32">
-        <f>SUM(D28:H28)</f>
-        <v>187469.56817653554</v>
-      </c>
-      <c r="K28" s="98"/>
-      <c r="L28" s="98"/>
-      <c r="M28" s="98"/>
-      <c r="N28" s="98"/>
-      <c r="O28" s="49"/>
-      <c r="P28" s="49"/>
-      <c r="Q28" s="49"/>
-      <c r="R28" s="49"/>
-      <c r="S28" s="49"/>
+    <row r="70" spans="2:11" ht="16.5">
+      <c r="C70" s="64"/>
+      <c r="D70" s="64"/>
+      <c r="E70" s="64"/>
+      <c r="F70" s="64"/>
+      <c r="G70" s="64"/>
+      <c r="H70" s="17"/>
+      <c r="I70" s="17"/>
+      <c r="J70" s="65"/>
     </row>
-    <row r="29" spans="2:19" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B29" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="29"/>
-      <c r="D29" s="30">
-        <v>63420.65</v>
-      </c>
-      <c r="E29" s="31">
-        <v>48094.167944272398</v>
-      </c>
-      <c r="F29" s="31">
-        <v>48091.435503910201</v>
-      </c>
-      <c r="G29" s="31">
-        <v>163092.739736155</v>
-      </c>
-      <c r="H29" s="31">
-        <v>232140.12130958401</v>
-      </c>
-      <c r="I29" s="32">
-        <f>SUM(D29:H29)</f>
-        <v>554839.11449392163</v>
-      </c>
-      <c r="K29" s="98"/>
-      <c r="L29" s="98"/>
-      <c r="M29" s="98"/>
-      <c r="N29" s="98"/>
-      <c r="O29" s="49"/>
-      <c r="P29" s="49"/>
-      <c r="Q29" s="49"/>
-      <c r="R29" s="49"/>
-      <c r="S29" s="49"/>
+    <row r="71" spans="2:11" ht="16.5">
+      <c r="C71" s="66"/>
+      <c r="D71" s="66"/>
+      <c r="E71" s="66"/>
+      <c r="F71" s="66"/>
+      <c r="H71" s="17"/>
+      <c r="I71" s="17"/>
+      <c r="J71" s="65"/>
     </row>
-    <row r="30" spans="2:19" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B30" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" s="29"/>
-      <c r="D30" s="30">
-        <v>400</v>
-      </c>
-      <c r="E30" s="31"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31"/>
-      <c r="I30" s="32">
-        <f>SUM(D30:H30)</f>
-        <v>400</v>
-      </c>
-      <c r="K30" s="49"/>
-      <c r="L30" s="49"/>
-      <c r="M30" s="99"/>
-      <c r="N30" s="99"/>
-      <c r="O30" s="100"/>
-      <c r="P30" s="49"/>
-      <c r="Q30" s="49"/>
-      <c r="R30" s="49"/>
-      <c r="S30" s="49"/>
+    <row r="72" spans="2:11" ht="16.5">
+      <c r="C72" s="33"/>
+      <c r="D72" s="33"/>
+      <c r="E72" s="33"/>
+      <c r="F72" s="33"/>
+      <c r="J72" s="65"/>
     </row>
-    <row r="31" spans="2:19" ht="15" customHeight="1">
-      <c r="B31" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="C31" s="36">
-        <v>1514946.3900000001</v>
-      </c>
-      <c r="D31" s="37">
-        <v>5620</v>
-      </c>
-      <c r="E31" s="38">
-        <v>200000</v>
-      </c>
-      <c r="F31" s="38">
-        <v>150000</v>
-      </c>
-      <c r="G31" s="38">
-        <v>59500</v>
-      </c>
-      <c r="H31" s="38">
-        <v>59500</v>
-      </c>
-      <c r="I31" s="41">
-        <f>SUM(D31:H31)</f>
-        <v>474620</v>
-      </c>
-      <c r="M31" s="99"/>
-      <c r="N31" s="101"/>
-      <c r="O31" s="101"/>
+    <row r="73" spans="2:11" ht="16.5">
+      <c r="C73" s="33"/>
+      <c r="D73" s="33"/>
+      <c r="E73" s="33"/>
+      <c r="F73" s="33"/>
+      <c r="J73" s="65"/>
     </row>
-    <row r="32" spans="2:19" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B32" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="29"/>
-      <c r="D32" s="30">
-        <v>0</v>
-      </c>
-      <c r="E32" s="31">
-        <v>200000</v>
-      </c>
-      <c r="F32" s="31">
-        <v>150000</v>
-      </c>
-      <c r="G32" s="31">
-        <v>59500</v>
-      </c>
-      <c r="H32" s="31">
-        <v>59500</v>
-      </c>
-      <c r="I32" s="32">
-        <f>SUM(D32:H32)</f>
-        <v>469000</v>
-      </c>
+    <row r="74" spans="2:11" ht="16.5">
+      <c r="J74" s="65"/>
     </row>
-    <row r="33" spans="2:12" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B33" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="29"/>
-      <c r="D33" s="30">
-        <v>0</v>
-      </c>
-      <c r="E33" s="31">
-        <v>0</v>
-      </c>
-      <c r="F33" s="31">
-        <v>0</v>
-      </c>
-      <c r="G33" s="31">
-        <v>0</v>
-      </c>
-      <c r="H33" s="31">
-        <v>0</v>
-      </c>
-      <c r="I33" s="32">
-        <f>SUM(D33:H33)</f>
-        <v>0</v>
-      </c>
+    <row r="75" spans="2:11" ht="16.5">
+      <c r="J75" s="65"/>
     </row>
-    <row r="34" spans="2:12" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B34" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="29"/>
-      <c r="D34" s="30">
-        <v>5579.8</v>
-      </c>
-      <c r="E34" s="31">
-        <v>0</v>
-      </c>
-      <c r="F34" s="31">
-        <v>0</v>
-      </c>
-      <c r="G34" s="31">
-        <v>0</v>
-      </c>
-      <c r="H34" s="31">
-        <v>0</v>
-      </c>
-      <c r="I34" s="32">
-        <f>SUM(D34:H34)</f>
-        <v>5579.8</v>
-      </c>
+    <row r="76" spans="2:11" ht="16.5">
+      <c r="J76" s="65"/>
     </row>
-    <row r="35" spans="2:12" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B35" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="29"/>
-      <c r="D35" s="30">
-        <v>0</v>
-      </c>
-      <c r="E35" s="31">
-        <v>0</v>
-      </c>
-      <c r="F35" s="31">
-        <v>0</v>
-      </c>
-      <c r="G35" s="31">
-        <v>0</v>
-      </c>
-      <c r="H35" s="31">
-        <v>0</v>
-      </c>
-      <c r="I35" s="32">
-        <f>SUM(D35:H35)</f>
-        <v>0</v>
-      </c>
+    <row r="77" spans="2:11" ht="16.5">
+      <c r="J77" s="65"/>
     </row>
-    <row r="36" spans="2:12" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B36" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="29"/>
-      <c r="D36" s="30">
-        <v>0</v>
-      </c>
-      <c r="E36" s="31">
-        <v>0</v>
-      </c>
-      <c r="F36" s="31">
-        <v>0</v>
-      </c>
-      <c r="G36" s="31">
-        <v>0</v>
-      </c>
-      <c r="H36" s="31">
-        <v>0</v>
-      </c>
-      <c r="I36" s="32">
-        <f>SUM(D36:H36)</f>
-        <v>0</v>
-      </c>
+    <row r="78" spans="2:11" ht="16.5">
+      <c r="J78" s="65"/>
     </row>
-    <row r="37" spans="2:12" ht="15" customHeight="1" outlineLevel="1">
-      <c r="B37" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" s="29"/>
-      <c r="D37" s="30">
-        <v>40.200000000000003</v>
-      </c>
-      <c r="E37" s="31"/>
-      <c r="F37" s="31"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="31"/>
-      <c r="I37" s="32">
-        <f>SUM(D37:H37)</f>
-        <v>40.200000000000003</v>
-      </c>
+    <row r="79" spans="2:11" ht="16.5">
+      <c r="J79" s="65"/>
     </row>
-    <row r="38" spans="2:12" ht="15" customHeight="1">
-      <c r="B38" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" s="51">
-        <v>832330.89</v>
-      </c>
-      <c r="D38" s="52">
-        <v>-6609.98</v>
-      </c>
-      <c r="E38" s="53">
-        <v>40000</v>
-      </c>
-      <c r="F38" s="53">
-        <v>0</v>
-      </c>
-      <c r="G38" s="53">
-        <v>0</v>
-      </c>
-      <c r="H38" s="53">
-        <v>40000</v>
-      </c>
-      <c r="I38" s="54">
-        <f>SUM(D38:H38)</f>
-        <v>73390.02</v>
-      </c>
+    <row r="80" spans="2:11" ht="16.5">
+      <c r="J80" s="65"/>
     </row>
-    <row r="39" spans="2:12" ht="15" customHeight="1">
-      <c r="B39" s="55" t="s">
-        <v>17</v>
-      </c>
-      <c r="C39" s="56">
-        <v>149791.74</v>
-      </c>
-      <c r="D39" s="57">
-        <v>6172.52</v>
-      </c>
-      <c r="E39" s="58">
-        <v>3745.453692149571</v>
-      </c>
-      <c r="F39" s="58">
-        <v>4344.4568996362541</v>
-      </c>
-      <c r="G39" s="58">
-        <v>8234.6025688529298</v>
-      </c>
-      <c r="H39" s="58">
-        <v>8064.4492106381022</v>
-      </c>
-      <c r="I39" s="59">
-        <f>SUM(D39:H39)</f>
-        <v>30561.482371276856</v>
-      </c>
+    <row r="81" spans="10:10" ht="16.5">
+      <c r="J81" s="65"/>
     </row>
-    <row r="40" spans="2:12" ht="15" customHeight="1">
-      <c r="B40" s="60" t="s">
-        <v>18</v>
-      </c>
-      <c r="C40" s="61">
-        <v>0.50071437003554498</v>
-      </c>
-      <c r="D40" s="62">
-        <f t="shared" ref="D40:I40" si="3">IFERROR(((D7+D15)-(D23+D31))/(D7+D15),0)</f>
-        <v>0.53630373841910273</v>
-      </c>
-      <c r="E40" s="63">
-        <f t="shared" si="3"/>
-        <v>0.54029026762224486</v>
-      </c>
-      <c r="F40" s="63">
-        <f t="shared" si="3"/>
-        <v>0.55099499017624232</v>
-      </c>
-      <c r="G40" s="63">
-        <f t="shared" si="3"/>
-        <v>0.59995667494802307</v>
-      </c>
-      <c r="H40" s="63">
-        <f t="shared" si="3"/>
-        <v>0.57695003831357139</v>
-      </c>
-      <c r="I40" s="61">
-        <f t="shared" si="3"/>
-        <v>0.57037060542518103</v>
-      </c>
+    <row r="82" spans="10:10" ht="16.5">
+      <c r="J82" s="65"/>
     </row>
-    <row r="41" spans="2:12" ht="15" customHeight="1">
-      <c r="B41" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="C41" s="45">
-        <v>9071015.4299999997</v>
-      </c>
-      <c r="D41" s="46">
-        <f t="shared" ref="D41:I41" si="4">SUM(D42:D44)</f>
-        <v>539013.98900000029</v>
-      </c>
-      <c r="E41" s="47">
-        <f t="shared" si="4"/>
-        <v>623134.37634510128</v>
-      </c>
-      <c r="F41" s="47">
-        <f t="shared" si="4"/>
-        <v>701382.85822907614</v>
-      </c>
-      <c r="G41" s="47">
-        <f t="shared" si="4"/>
-        <v>1333493.5720040328</v>
-      </c>
-      <c r="H41" s="47">
-        <f t="shared" si="4"/>
-        <v>1213704.2374957125</v>
-      </c>
-      <c r="I41" s="48">
-        <f t="shared" si="4"/>
-        <v>4410729.0330739226</v>
-      </c>
-      <c r="K41" s="49"/>
-    </row>
-    <row r="42" spans="2:12" ht="15" customHeight="1">
-      <c r="B42" s="64" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="65">
-        <v>8348947.9700000007</v>
-      </c>
-      <c r="D42" s="66">
-        <v>534595.81900000025</v>
-      </c>
-      <c r="E42" s="67">
-        <v>520951.546156422</v>
-      </c>
-      <c r="F42" s="67">
-        <v>624751.53747435915</v>
-      </c>
-      <c r="G42" s="67">
-        <v>1303091.68521158</v>
-      </c>
-      <c r="H42" s="67">
-        <v>1183302.3507032597</v>
-      </c>
-      <c r="I42" s="68">
-        <f>SUM(D42:H42)</f>
-        <v>4166692.938545621</v>
-      </c>
-      <c r="K42" s="49"/>
-    </row>
-    <row r="43" spans="2:12" ht="15" customHeight="1">
-      <c r="B43" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="C43" s="51">
-        <v>828369.69000000006</v>
-      </c>
-      <c r="D43" s="52">
-        <v>4418.17</v>
-      </c>
-      <c r="E43" s="53">
-        <v>102182.83018867925</v>
-      </c>
-      <c r="F43" s="53">
-        <v>76631.320754716988</v>
-      </c>
-      <c r="G43" s="53">
-        <v>30401.886792452831</v>
-      </c>
-      <c r="H43" s="53">
-        <v>30401.886792452831</v>
-      </c>
-      <c r="I43" s="54">
-        <f>SUM(D43:H43)</f>
-        <v>244036.09452830191</v>
-      </c>
-    </row>
-    <row r="44" spans="2:12" ht="15" customHeight="1">
-      <c r="B44" s="55" t="s">
-        <v>17</v>
-      </c>
-      <c r="C44" s="56">
-        <v>-106302.23</v>
-      </c>
-      <c r="D44" s="57">
-        <v>0</v>
-      </c>
-      <c r="E44" s="58">
-        <v>0</v>
-      </c>
-      <c r="F44" s="58">
-        <v>0</v>
-      </c>
-      <c r="G44" s="58">
-        <v>0</v>
-      </c>
-      <c r="H44" s="58">
-        <v>0</v>
-      </c>
-      <c r="I44" s="59">
-        <f>SUM(D44:H44)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:12" ht="15" customHeight="1">
-      <c r="B45" s="60" t="s">
-        <v>21</v>
-      </c>
-      <c r="C45" s="69">
-        <v>4.7656400944499939</v>
-      </c>
-      <c r="D45" s="70">
-        <f t="shared" ref="D45:I45" si="5">IFERROR((D15+D7)/(D42+D43),0)</f>
-        <v>4.7048222342147756</v>
-      </c>
-      <c r="E45" s="71">
-        <f t="shared" si="5"/>
-        <v>5.056481966695463</v>
-      </c>
-      <c r="F45" s="71">
-        <f t="shared" si="5"/>
-        <v>5.0747170204995102</v>
-      </c>
-      <c r="G45" s="71">
-        <f t="shared" si="5"/>
-        <v>5.2569878593629058</v>
-      </c>
-      <c r="H45" s="71">
-        <f t="shared" si="5"/>
-        <v>5.3512697157481792</v>
-      </c>
-      <c r="I45" s="72">
-        <f t="shared" si="5"/>
-        <v>5.1581428701034255</v>
-      </c>
-    </row>
-    <row r="46" spans="2:12" ht="15" customHeight="1">
-      <c r="B46" s="73" t="s">
-        <v>22</v>
-      </c>
-      <c r="C46" s="74">
-        <v>13747760.16</v>
-      </c>
-      <c r="D46" s="75">
-        <f t="shared" ref="D46:H46" si="6">D22-D41</f>
-        <v>636466.04099999997</v>
-      </c>
-      <c r="E46" s="76">
-        <f t="shared" si="6"/>
-        <v>869095.64139690739</v>
-      </c>
-      <c r="F46" s="76">
-        <f t="shared" si="6"/>
-        <v>901113.89854931307</v>
-      </c>
-      <c r="G46" s="76">
-        <f t="shared" si="6"/>
-        <v>1479108.5535157979</v>
-      </c>
-      <c r="H46" s="76">
-        <f t="shared" si="6"/>
-        <v>1582009.948594287</v>
-      </c>
-      <c r="I46" s="77">
-        <f>SUM(D46:H46)</f>
-        <v>5467794.0830563055</v>
-      </c>
-    </row>
-    <row r="47" spans="2:12" ht="15" customHeight="1">
-      <c r="B47" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="C47" s="79">
-        <v>0.60247580356698716</v>
-      </c>
-      <c r="D47" s="80">
-        <f t="shared" ref="D47:I47" si="7">IFERROR(D46/D$22,0)</f>
-        <v>0.54145202364688394</v>
-      </c>
-      <c r="E47" s="81">
-        <f t="shared" si="7"/>
-        <v>0.58241399185361054</v>
-      </c>
-      <c r="F47" s="81">
-        <f t="shared" si="7"/>
-        <v>0.56231870344679202</v>
-      </c>
-      <c r="G47" s="81">
-        <f t="shared" si="7"/>
-        <v>0.52588616786401177</v>
-      </c>
-      <c r="H47" s="81">
-        <f t="shared" si="7"/>
-        <v>0.56586970029537886</v>
-      </c>
-      <c r="I47" s="79">
-        <f t="shared" si="7"/>
-        <v>0.55350319261066194</v>
-      </c>
-      <c r="K47" s="2"/>
-      <c r="L47" s="2"/>
-    </row>
-    <row r="48" spans="2:12" ht="15" customHeight="1">
-      <c r="B48" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="45">
-        <v>8570185.5200000014</v>
-      </c>
-      <c r="D48" s="46">
-        <f t="shared" ref="D48:I48" si="8">SUM(D49:D53)</f>
-        <v>694998.08000000007</v>
-      </c>
-      <c r="E48" s="47">
-        <f t="shared" si="8"/>
-        <v>663631.97002070153</v>
-      </c>
-      <c r="F48" s="47">
-        <f t="shared" si="8"/>
-        <v>769765.35500055028</v>
-      </c>
-      <c r="G48" s="47">
-        <f t="shared" si="8"/>
-        <v>1459034.3318245916</v>
-      </c>
-      <c r="H48" s="47">
-        <f t="shared" si="8"/>
-        <v>1428885.9926382275</v>
-      </c>
-      <c r="I48" s="48">
-        <f t="shared" si="8"/>
-        <v>5016315.729484072</v>
-      </c>
-      <c r="K48" s="2"/>
-      <c r="L48" s="2"/>
-    </row>
-    <row r="49" spans="2:12" ht="15" customHeight="1">
-      <c r="B49" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="C49" s="65">
-        <v>3994149.0400000005</v>
-      </c>
-      <c r="D49" s="66">
-        <v>297887.73000000004</v>
-      </c>
-      <c r="E49" s="67">
-        <v>282844.17798549513</v>
-      </c>
-      <c r="F49" s="67">
-        <v>328078.90353753115</v>
-      </c>
-      <c r="G49" s="67">
-        <v>621849.73732454376</v>
-      </c>
-      <c r="H49" s="67">
-        <v>609000.32289002067</v>
-      </c>
-      <c r="I49" s="68">
-        <f>SUM(D49:H49)</f>
-        <v>2139660.871737591</v>
-      </c>
-      <c r="K49" s="2"/>
-      <c r="L49" s="2"/>
-    </row>
-    <row r="50" spans="2:12" ht="15" customHeight="1">
-      <c r="B50" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="C50" s="51">
-        <v>1243576.5100000002</v>
-      </c>
-      <c r="D50" s="52">
-        <v>153577.63</v>
-      </c>
-      <c r="E50" s="53">
-        <v>112363.61076448712</v>
-      </c>
-      <c r="F50" s="53">
-        <v>130333.70698908762</v>
-      </c>
-      <c r="G50" s="53">
-        <v>247038.07706558789</v>
-      </c>
-      <c r="H50" s="53">
-        <v>241933.47631914305</v>
-      </c>
-      <c r="I50" s="54">
-        <f>SUM(D50:H50)</f>
-        <v>885246.50113830576</v>
-      </c>
-    </row>
-    <row r="51" spans="2:12" ht="15" customHeight="1">
-      <c r="B51" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="C51" s="51">
-        <v>1346255.71</v>
-      </c>
-      <c r="D51" s="52">
-        <v>117480.4</v>
-      </c>
-      <c r="E51" s="53">
-        <v>118606.03358473642</v>
-      </c>
-      <c r="F51" s="53">
-        <v>137574.46848848139</v>
-      </c>
-      <c r="G51" s="53">
-        <v>260762.41468034277</v>
-      </c>
-      <c r="H51" s="53">
-        <v>255374.2250035399</v>
-      </c>
-      <c r="I51" s="54">
-        <f>SUM(D51:H51)</f>
-        <v>889797.54175710049</v>
-      </c>
-    </row>
-    <row r="52" spans="2:12" ht="15" customHeight="1">
-      <c r="B52" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="C52" s="51">
-        <v>1986204.26</v>
-      </c>
-      <c r="D52" s="52">
-        <v>126052.32</v>
-      </c>
-      <c r="E52" s="53">
-        <v>149818.14768598284</v>
-      </c>
-      <c r="F52" s="53">
-        <v>173778.27598545016</v>
-      </c>
-      <c r="G52" s="53">
-        <v>329384.10275411716</v>
-      </c>
-      <c r="H52" s="53">
-        <v>322577.96842552407</v>
-      </c>
-      <c r="I52" s="54">
-        <f>SUM(D52:H52)</f>
-        <v>1101610.814851074</v>
-      </c>
-    </row>
-    <row r="53" spans="2:12" ht="15" customHeight="1">
-      <c r="B53" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="C53" s="51">
-        <v>0</v>
-      </c>
-      <c r="D53" s="52">
-        <v>0</v>
-      </c>
-      <c r="E53" s="53">
-        <v>0</v>
-      </c>
-      <c r="F53" s="53">
-        <v>0</v>
-      </c>
-      <c r="G53" s="53">
-        <v>0</v>
-      </c>
-      <c r="H53" s="53">
-        <v>0</v>
-      </c>
-      <c r="I53" s="54">
-        <f>SUM(D53:H53)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="2:12" ht="15" customHeight="1">
-      <c r="B54" s="73" t="s">
-        <v>29</v>
-      </c>
-      <c r="C54" s="74">
-        <v>5177574.6399999987</v>
-      </c>
-      <c r="D54" s="75">
-        <f t="shared" ref="D54:I54" si="9">D46-D48</f>
-        <v>-58532.039000000106</v>
-      </c>
-      <c r="E54" s="76">
-        <f t="shared" si="9"/>
-        <v>205463.67137620586</v>
-      </c>
-      <c r="F54" s="76">
-        <f t="shared" si="9"/>
-        <v>131348.5435487628</v>
-      </c>
-      <c r="G54" s="76">
-        <f t="shared" si="9"/>
-        <v>20074.22169120633</v>
-      </c>
-      <c r="H54" s="76">
-        <f t="shared" si="9"/>
-        <v>153123.95595605951</v>
-      </c>
-      <c r="I54" s="77">
-        <f t="shared" si="9"/>
-        <v>451478.35357223358</v>
-      </c>
-    </row>
-    <row r="55" spans="2:12" ht="15" customHeight="1">
-      <c r="B55" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="C55" s="79">
-        <v>0.22689975715739089</v>
-      </c>
-      <c r="D55" s="80">
-        <f t="shared" ref="D55:I55" si="10">IFERROR(D54/D$22,0)</f>
-        <v>-4.9794158561758034E-2</v>
-      </c>
-      <c r="E55" s="81">
-        <f t="shared" si="10"/>
-        <v>0.13768900835214831</v>
-      </c>
-      <c r="F55" s="81">
-        <f t="shared" si="10"/>
-        <v>8.1964935650055179E-2</v>
-      </c>
-      <c r="G55" s="81">
-        <f t="shared" si="10"/>
-        <v>7.1372418832600336E-3</v>
-      </c>
-      <c r="H55" s="81">
-        <f t="shared" si="10"/>
-        <v>5.4770962181300085E-2</v>
-      </c>
-      <c r="I55" s="79">
-        <f t="shared" si="10"/>
-        <v>4.5703021419774122E-2</v>
-      </c>
-    </row>
-    <row r="56" spans="2:12" ht="15" customHeight="1">
-      <c r="B56" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="C56" s="45">
-        <v>7116475.8399999989</v>
-      </c>
-      <c r="D56" s="46">
-        <f t="shared" ref="D56:I56" si="11">SUM(D57:D64)</f>
-        <v>575806.25</v>
-      </c>
-      <c r="E56" s="47">
-        <f t="shared" si="11"/>
-        <v>560530.41662807029</v>
-      </c>
-      <c r="F56" s="47">
-        <f t="shared" si="11"/>
-        <v>604950.61773333338</v>
-      </c>
-      <c r="G56" s="47">
-        <f t="shared" si="11"/>
-        <v>648505.95773333334</v>
-      </c>
-      <c r="H56" s="47">
-        <f t="shared" si="11"/>
-        <v>633665.61773333338</v>
-      </c>
-      <c r="I56" s="48">
-        <f t="shared" si="11"/>
-        <v>3023458.8598280698</v>
-      </c>
-    </row>
-    <row r="57" spans="2:12" ht="15" customHeight="1">
-      <c r="B57" s="64" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="65">
-        <v>4137336.4699999997</v>
-      </c>
-      <c r="D57" s="66">
-        <v>321920.38</v>
-      </c>
-      <c r="E57" s="67">
-        <v>347835.1266280702</v>
-      </c>
-      <c r="F57" s="67">
-        <v>353895.66773333331</v>
-      </c>
-      <c r="G57" s="67">
-        <v>383310.66773333331</v>
-      </c>
-      <c r="H57" s="67">
-        <v>368110.66773333331</v>
-      </c>
-      <c r="I57" s="68">
-        <f>SUM(D57:H57)</f>
-        <v>1775072.5098280702</v>
-      </c>
-    </row>
-    <row r="58" spans="2:12" ht="15" customHeight="1">
-      <c r="B58" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="C58" s="51">
-        <v>1037190.7500000001</v>
-      </c>
-      <c r="D58" s="52">
-        <v>51469</v>
-      </c>
-      <c r="E58" s="53">
-        <v>50000</v>
-      </c>
-      <c r="F58" s="53">
-        <v>50000</v>
-      </c>
-      <c r="G58" s="53">
-        <v>50000</v>
-      </c>
-      <c r="H58" s="53">
-        <v>50000</v>
-      </c>
-      <c r="I58" s="54">
-        <f>SUM(D58:H58)</f>
-        <v>251469</v>
-      </c>
-    </row>
-    <row r="59" spans="2:12" ht="15" customHeight="1">
-      <c r="B59" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="C59" s="51">
-        <v>67586.23</v>
-      </c>
-      <c r="D59" s="52">
-        <v>3717.73</v>
-      </c>
-      <c r="E59" s="53">
-        <v>3500</v>
-      </c>
-      <c r="F59" s="53">
-        <v>3500</v>
-      </c>
-      <c r="G59" s="53">
-        <v>3500</v>
-      </c>
-      <c r="H59" s="53">
-        <v>3500</v>
-      </c>
-      <c r="I59" s="54">
-        <f>SUM(D59:H59)</f>
-        <v>17717.73</v>
-      </c>
-    </row>
-    <row r="60" spans="2:12" ht="15" customHeight="1">
-      <c r="B60" s="50" t="s">
-        <v>34</v>
-      </c>
-      <c r="C60" s="51">
-        <v>295941.65999999992</v>
-      </c>
-      <c r="D60" s="52">
-        <v>24699.25</v>
-      </c>
-      <c r="E60" s="53">
-        <v>23987.63</v>
-      </c>
-      <c r="F60" s="53">
-        <v>26847.289999999997</v>
-      </c>
-      <c r="G60" s="53">
-        <v>23987.63</v>
-      </c>
-      <c r="H60" s="53">
-        <v>26847.289999999997</v>
-      </c>
-      <c r="I60" s="54">
-        <f>SUM(D60:H60)</f>
-        <v>126369.09</v>
-      </c>
-    </row>
-    <row r="61" spans="2:12" ht="15" customHeight="1">
-      <c r="B61" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="C61" s="51">
-        <v>152321.34999999998</v>
-      </c>
-      <c r="D61" s="52">
-        <v>2000.3</v>
-      </c>
-      <c r="E61" s="53">
-        <v>2000</v>
-      </c>
-      <c r="F61" s="53">
-        <v>37500</v>
-      </c>
-      <c r="G61" s="53">
-        <v>4500</v>
-      </c>
-      <c r="H61" s="53">
-        <v>2000</v>
-      </c>
-      <c r="I61" s="54">
-        <f>SUM(D61:H61)</f>
-        <v>48000.3</v>
-      </c>
-    </row>
-    <row r="62" spans="2:12" ht="15" customHeight="1">
-      <c r="B62" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="C62" s="51">
-        <v>1268119.6799999992</v>
-      </c>
-      <c r="D62" s="52">
-        <v>150501.71000000002</v>
-      </c>
-      <c r="E62" s="53">
-        <v>100000</v>
-      </c>
-      <c r="F62" s="53">
-        <v>100000</v>
-      </c>
-      <c r="G62" s="53">
-        <v>150000</v>
-      </c>
-      <c r="H62" s="53">
-        <v>150000</v>
-      </c>
-      <c r="I62" s="54">
-        <f>SUM(D62:H62)</f>
-        <v>650501.71</v>
-      </c>
-    </row>
-    <row r="63" spans="2:12" ht="15" customHeight="1">
-      <c r="B63" s="50" t="s">
-        <v>36</v>
-      </c>
-      <c r="C63" s="51">
-        <v>45286.460000000006</v>
-      </c>
-      <c r="D63" s="52">
-        <v>3893.6400000000003</v>
-      </c>
-      <c r="E63" s="53">
-        <v>8207.66</v>
-      </c>
-      <c r="F63" s="53">
-        <v>8207.66</v>
-      </c>
-      <c r="G63" s="53">
-        <v>8207.66</v>
-      </c>
-      <c r="H63" s="53">
-        <v>8207.66</v>
-      </c>
-      <c r="I63" s="54">
-        <f>SUM(D63:H63)</f>
-        <v>36724.28</v>
-      </c>
-    </row>
-    <row r="64" spans="2:12" ht="15" customHeight="1">
-      <c r="B64" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="C64" s="51">
-        <v>112693.24000000002</v>
-      </c>
-      <c r="D64" s="52">
-        <v>17604.239999999998</v>
-      </c>
-      <c r="E64" s="53">
-        <v>25000</v>
-      </c>
-      <c r="F64" s="53">
-        <v>25000</v>
-      </c>
-      <c r="G64" s="53">
-        <v>25000</v>
-      </c>
-      <c r="H64" s="53">
-        <v>25000</v>
-      </c>
-      <c r="I64" s="54">
-        <f>SUM(D64:H64)</f>
-        <v>117604.23999999999</v>
-      </c>
-    </row>
-    <row r="65" spans="2:9" ht="15" customHeight="1">
-      <c r="B65" s="73" t="s">
-        <v>37</v>
-      </c>
-      <c r="C65" s="74">
-        <v>-1938901.2000000002</v>
-      </c>
-      <c r="D65" s="75">
-        <f t="shared" ref="D65:I65" si="12">D54-D56</f>
-        <v>-634338.28900000011</v>
-      </c>
-      <c r="E65" s="76">
-        <f t="shared" si="12"/>
-        <v>-355066.74525186443</v>
-      </c>
-      <c r="F65" s="76">
-        <f t="shared" si="12"/>
-        <v>-473602.07418457058</v>
-      </c>
-      <c r="G65" s="76">
-        <f t="shared" si="12"/>
-        <v>-628431.73604212701</v>
-      </c>
-      <c r="H65" s="76">
-        <f t="shared" si="12"/>
-        <v>-480541.66177727387</v>
-      </c>
-      <c r="I65" s="77">
-        <f t="shared" si="12"/>
-        <v>-2571980.5062558362</v>
-      </c>
-    </row>
-    <row r="66" spans="2:9" ht="15" customHeight="1">
-      <c r="B66" s="82" t="s">
-        <v>23</v>
-      </c>
-      <c r="C66" s="83">
-        <v>-8.4969554670132952E-2</v>
-      </c>
-      <c r="D66" s="84">
-        <f t="shared" ref="D66:I66" si="13">IFERROR(D65/D$22,0)</f>
-        <v>-0.53964191037766929</v>
-      </c>
-      <c r="E66" s="85">
-        <f t="shared" si="13"/>
-        <v>-0.23794370909998128</v>
-      </c>
-      <c r="F66" s="85">
-        <f t="shared" si="13"/>
-        <v>-0.29554011400103286</v>
-      </c>
-      <c r="G66" s="85">
-        <f t="shared" si="13"/>
-        <v>-0.2234342818488694</v>
-      </c>
-      <c r="H66" s="85">
-        <f t="shared" si="13"/>
-        <v>-0.17188511764478498</v>
-      </c>
-      <c r="I66" s="83">
-        <f t="shared" si="13"/>
-        <v>-0.26036083289172618</v>
-      </c>
-    </row>
-    <row r="67" spans="2:9" ht="15" hidden="1" customHeight="1">
-      <c r="B67" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="C67" s="45" t="e">
-        <f t="shared" ref="C67:I67" si="14">SUM(C68:C75)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D67" s="86">
-        <f t="shared" si="14"/>
-        <v>315277.73</v>
-      </c>
-      <c r="E67" s="86">
-        <f t="shared" si="14"/>
-        <v>194845.24380144037</v>
-      </c>
-      <c r="F67" s="86">
-        <f t="shared" si="14"/>
-        <v>177868.99201614523</v>
-      </c>
-      <c r="G67" s="86">
-        <f t="shared" si="14"/>
-        <v>235344.72378092696</v>
-      </c>
-      <c r="H67" s="87">
-        <f t="shared" si="14"/>
-        <v>237206.71890801005</v>
-      </c>
-      <c r="I67" s="45">
-        <f t="shared" si="14"/>
-        <v>1160543.4085065224</v>
-      </c>
-    </row>
-    <row r="68" spans="2:9" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="B68" s="64" t="s">
-        <v>39</v>
-      </c>
-      <c r="C68" s="65" t="e">
-        <f>SUM(#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D68" s="88">
-        <v>154382.56</v>
-      </c>
-      <c r="E68" s="88">
-        <v>76666.666666666672</v>
-      </c>
-      <c r="F68" s="88">
-        <v>76666.666666666672</v>
-      </c>
-      <c r="G68" s="88">
-        <v>76666.666666666672</v>
-      </c>
-      <c r="H68" s="89">
-        <v>76666.666666666672</v>
-      </c>
-      <c r="I68" s="65">
-        <f>SUM(D68:H68)</f>
-        <v>461049.22666666674</v>
-      </c>
-    </row>
-    <row r="69" spans="2:9" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="B69" s="50" t="s">
-        <v>40</v>
-      </c>
-      <c r="C69" s="51" t="e">
-        <f>SUM(#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D69" s="90">
-        <v>-321.13</v>
-      </c>
-      <c r="E69" s="90">
-        <v>0</v>
-      </c>
-      <c r="F69" s="90">
-        <v>0</v>
-      </c>
-      <c r="G69" s="90">
-        <v>0</v>
-      </c>
-      <c r="H69" s="91">
-        <v>0</v>
-      </c>
-      <c r="I69" s="51">
-        <f>SUM(D69:H69)</f>
-        <v>-321.13</v>
-      </c>
-    </row>
-    <row r="70" spans="2:9" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="B70" s="50" t="s">
-        <v>41</v>
-      </c>
-      <c r="C70" s="51" t="e">
-        <f>SUM(#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D70" s="90">
-        <v>96397.43</v>
-      </c>
-      <c r="E70" s="90">
-        <v>0</v>
-      </c>
-      <c r="F70" s="90">
-        <v>0</v>
-      </c>
-      <c r="G70" s="90">
-        <v>0</v>
-      </c>
-      <c r="H70" s="91">
-        <v>0</v>
-      </c>
-      <c r="I70" s="51">
-        <f>SUM(D70:H70)</f>
-        <v>96397.43</v>
-      </c>
-    </row>
-    <row r="71" spans="2:9" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="B71" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="C71" s="51" t="e">
-        <f>SUM(#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D71" s="90">
-        <v>0</v>
-      </c>
-      <c r="E71" s="90">
-        <v>0</v>
-      </c>
-      <c r="F71" s="90">
-        <v>0</v>
-      </c>
-      <c r="G71" s="90">
-        <v>0</v>
-      </c>
-      <c r="H71" s="91">
-        <v>0</v>
-      </c>
-      <c r="I71" s="51">
-        <f>SUM(D71:H71)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="2:9" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="B72" s="50" t="s">
-        <v>43</v>
-      </c>
-      <c r="C72" s="51" t="e">
-        <f>SUM(#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D72" s="90">
-        <v>7099.69</v>
-      </c>
-      <c r="E72" s="90">
-        <v>3000</v>
-      </c>
-      <c r="F72" s="90">
-        <v>3000</v>
-      </c>
-      <c r="G72" s="90">
-        <v>3000</v>
-      </c>
-      <c r="H72" s="91">
-        <v>3000</v>
-      </c>
-      <c r="I72" s="51">
-        <f>SUM(D72:H72)</f>
-        <v>19099.689999999999</v>
-      </c>
-    </row>
-    <row r="73" spans="2:9" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="B73" s="50" t="s">
-        <v>44</v>
-      </c>
-      <c r="C73" s="51" t="e">
-        <f>SUM(#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D73" s="90">
-        <v>74250</v>
-      </c>
-      <c r="E73" s="90">
-        <v>110195.1371347737</v>
-      </c>
-      <c r="F73" s="90">
-        <v>93218.885349478558</v>
-      </c>
-      <c r="G73" s="90">
-        <v>150694.6171142603</v>
-      </c>
-      <c r="H73" s="91">
-        <v>152556.61224134336</v>
-      </c>
-      <c r="I73" s="51">
-        <f>SUM(D73:H73)</f>
-        <v>580915.25183985592</v>
-      </c>
-    </row>
-    <row r="74" spans="2:9" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="B74" s="50" t="s">
-        <v>45</v>
-      </c>
-      <c r="C74" s="51" t="e">
-        <f>SUM(#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D74" s="90">
-        <v>-16530.82</v>
-      </c>
-      <c r="E74" s="90">
-        <v>4983.4399999999996</v>
-      </c>
-      <c r="F74" s="90">
-        <v>4983.4399999999996</v>
-      </c>
-      <c r="G74" s="90">
-        <v>4983.4399999999996</v>
-      </c>
-      <c r="H74" s="91">
-        <v>4983.4399999999996</v>
-      </c>
-      <c r="I74" s="51">
-        <f>SUM(D74:H74)</f>
-        <v>3402.9399999999978</v>
-      </c>
-    </row>
-    <row r="75" spans="2:9" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="B75" s="50" t="s">
-        <v>46</v>
-      </c>
-      <c r="C75" s="51" t="e">
-        <f>SUM(#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D75" s="90">
-        <v>0</v>
-      </c>
-      <c r="E75" s="90">
-        <v>0</v>
-      </c>
-      <c r="F75" s="90">
-        <v>0</v>
-      </c>
-      <c r="G75" s="90">
-        <v>0</v>
-      </c>
-      <c r="H75" s="91">
-        <v>0</v>
-      </c>
-      <c r="I75" s="51">
-        <f>SUM(D75:H75)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="2:9" ht="15" hidden="1" customHeight="1" collapsed="1">
-      <c r="B76" s="73" t="s">
-        <v>47</v>
-      </c>
-      <c r="C76" s="74" t="e">
-        <f>C65+C67</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D76" s="92">
-        <f t="shared" ref="D76:I76" si="15">D65-D67</f>
-        <v>-949616.01900000009</v>
-      </c>
-      <c r="E76" s="92">
-        <f t="shared" si="15"/>
-        <v>-549911.98905330477</v>
-      </c>
-      <c r="F76" s="92">
-        <f t="shared" si="15"/>
-        <v>-651471.06620071584</v>
-      </c>
-      <c r="G76" s="92">
-        <f t="shared" si="15"/>
-        <v>-863776.45982305403</v>
-      </c>
-      <c r="H76" s="93">
-        <f t="shared" si="15"/>
-        <v>-717748.38068528392</v>
-      </c>
-      <c r="I76" s="74">
-        <f t="shared" si="15"/>
-        <v>-3732523.9147623586</v>
-      </c>
-    </row>
-    <row r="77" spans="2:9" ht="15" hidden="1" customHeight="1">
-      <c r="B77" s="82" t="s">
-        <v>23</v>
-      </c>
-      <c r="C77" s="94">
-        <f t="shared" ref="C77:I77" si="16">IFERROR(C76/C$22,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D77" s="95">
-        <f t="shared" si="16"/>
-        <v>-0.80785380845644816</v>
-      </c>
-      <c r="E77" s="95">
-        <f t="shared" si="16"/>
-        <v>-0.36851690591602809</v>
-      </c>
-      <c r="F77" s="95">
-        <f t="shared" si="16"/>
-        <v>-0.40653502944393688</v>
-      </c>
-      <c r="G77" s="95">
-        <f t="shared" si="16"/>
-        <v>-0.30710936750906748</v>
-      </c>
-      <c r="H77" s="96">
-        <f t="shared" si="16"/>
-        <v>-0.25673167316473966</v>
-      </c>
-      <c r="I77" s="94">
-        <f t="shared" si="16"/>
-        <v>-0.37784230202060026</v>
-      </c>
-    </row>
-    <row r="78" spans="2:9" collapsed="1">
-      <c r="D78" s="49"/>
-    </row>
-    <row r="80" spans="2:9">
-      <c r="D80" s="102"/>
-      <c r="E80" s="102"/>
-      <c r="F80" s="102"/>
-      <c r="G80" s="102"/>
-      <c r="H80" s="102"/>
-      <c r="I80" s="102"/>
-    </row>
-    <row r="81" spans="4:13">
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
-      <c r="M81" s="103"/>
-    </row>
-    <row r="82" spans="4:13" ht="16.5">
-      <c r="D82" s="104"/>
-      <c r="E82" s="104"/>
-      <c r="F82" s="104"/>
-      <c r="G82" s="104"/>
-      <c r="H82" s="104"/>
-      <c r="I82" s="104"/>
-      <c r="L82" s="105"/>
-    </row>
-    <row r="83" spans="4:13" ht="16.5">
-      <c r="D83" s="106"/>
-      <c r="E83" s="106"/>
-      <c r="F83" s="106"/>
-      <c r="G83" s="106"/>
-      <c r="H83" s="106"/>
-      <c r="L83" s="105"/>
-    </row>
-    <row r="84" spans="4:13" ht="16.5">
-      <c r="D84" s="107"/>
-      <c r="E84" s="49"/>
-      <c r="F84" s="49"/>
-      <c r="G84" s="49"/>
-      <c r="H84" s="49"/>
-      <c r="L84" s="105"/>
-    </row>
-    <row r="85" spans="4:13" ht="16.5">
-      <c r="D85" s="49"/>
-      <c r="E85" s="49"/>
-      <c r="F85" s="49"/>
-      <c r="G85" s="49"/>
-      <c r="H85" s="49"/>
-      <c r="L85" s="105"/>
-    </row>
-    <row r="86" spans="4:13" ht="16.5">
-      <c r="L86" s="105"/>
-    </row>
-    <row r="87" spans="4:13" ht="16.5">
-      <c r="L87" s="105"/>
-    </row>
-    <row r="88" spans="4:13" ht="16.5">
-      <c r="L88" s="105"/>
-    </row>
-    <row r="89" spans="4:13" ht="16.5">
-      <c r="L89" s="105"/>
-    </row>
-    <row r="90" spans="4:13" ht="16.5">
-      <c r="L90" s="105"/>
-    </row>
-    <row r="91" spans="4:13" ht="16.5">
-      <c r="L91" s="105"/>
-    </row>
-    <row r="92" spans="4:13" ht="16.5">
-      <c r="L92" s="105"/>
-    </row>
-    <row r="93" spans="4:13" ht="16.5">
-      <c r="L93" s="105"/>
-    </row>
-    <row r="94" spans="4:13" ht="16.5">
-      <c r="L94" s="105"/>
-    </row>
-    <row r="95" spans="4:13" ht="16.5">
-      <c r="L95" s="105"/>
-    </row>
-    <row r="107" spans="3:4">
-      <c r="C107" s="1">
-        <v>214773</v>
-      </c>
-      <c r="D107" s="108"/>
-    </row>
-    <row r="108" spans="3:4">
-      <c r="D108" s="108"/>
+    <row r="83" spans="10:10" ht="16.5">
+      <c r="J83" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/frontend/public/data/old_new_pl.xlsx
+++ b/frontend/public/data/old_new_pl.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\업무인수인계\6.실적보고\2025년\stodashboard\frontend\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57752B8E-1142-4A00-973E-11D1091FF1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66E3F87-EF96-47F1-A9D5-38DD5D392909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="15" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{0C279A8B-39A3-4ED4-B4B9-CA68FBFF28CA}"/>
   </bookViews>
@@ -19897,7 +19897,10 @@
         <f t="shared" si="15"/>
         <v>-1937642.2172558359</v>
       </c>
-      <c r="H65" s="17"/>
+      <c r="H65" s="17">
+        <f>G65-old!G65</f>
+        <v>-3796987.2655365765</v>
+      </c>
       <c r="I65" s="17"/>
     </row>
     <row r="66" spans="2:11" ht="15" customHeight="1">
